--- a/docs/martial_arts/武功強度設定表.xlsx
+++ b/docs/martial_arts/武功強度設定表.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>範例中的命中、防守、內力數字取自目前遊戲裡的三門刀法；傷害加成、解鎖等級、特效是建議值，尚未定案。
+          <t>範例是新版三門刀法（5 招），所有數字都是建議值，尚未定案。
 傷害加成、解鎖等級、消耗、冷卻、特效、出招條件都是新機制（NEW），要等引擎做好才會生效。</t>
         </is>
       </c>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:N201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -699,7 +699,13 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -744,6 +750,41 @@
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
+          <t>武術造詣
+係數</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>武學之道
+起始等級</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>武學之道
+係數</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>整套特效</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>整套特效
+機率 (%)</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>整套特效
+強度</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
@@ -770,7 +811,7 @@
         </is>
       </c>
       <c r="E2" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
@@ -781,9 +822,29 @@
         <f>IF(A2="","",COUNTIF(招式表!$A$2:$A$201,A2))</f>
         <v/>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>範例：取自現有三門刀法</t>
+      <c r="H2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>三招重演</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>範例：數字皆為建議值</t>
         </is>
       </c>
     </row>
@@ -798,7 +859,13 @@
         <f>IF(A3="","",COUNTIF(招式表!$A$2:$A$201,A3))</f>
         <v/>
       </c>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -811,7 +878,13 @@
         <f>IF(A4="","",COUNTIF(招式表!$A$2:$A$201,A4))</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n"/>
@@ -824,7 +897,13 @@
         <f>IF(A5="","",COUNTIF(招式表!$A$2:$A$201,A5))</f>
         <v/>
       </c>
-      <c r="H5" s="14" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -837,7 +916,13 @@
         <f>IF(A6="","",COUNTIF(招式表!$A$2:$A$201,A6))</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n"/>
@@ -850,7 +935,13 @@
         <f>IF(A7="","",COUNTIF(招式表!$A$2:$A$201,A7))</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -863,7 +954,13 @@
         <f>IF(A8="","",COUNTIF(招式表!$A$2:$A$201,A8))</f>
         <v/>
       </c>
-      <c r="H8" s="14" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n"/>
@@ -876,7 +973,13 @@
         <f>IF(A9="","",COUNTIF(招式表!$A$2:$A$201,A9))</f>
         <v/>
       </c>
-      <c r="H9" s="14" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -889,7 +992,13 @@
         <f>IF(A10="","",COUNTIF(招式表!$A$2:$A$201,A10))</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n"/>
@@ -902,7 +1011,13 @@
         <f>IF(A11="","",COUNTIF(招式表!$A$2:$A$201,A11))</f>
         <v/>
       </c>
-      <c r="H11" s="14" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -915,7 +1030,13 @@
         <f>IF(A12="","",COUNTIF(招式表!$A$2:$A$201,A12))</f>
         <v/>
       </c>
-      <c r="H12" s="14" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n"/>
@@ -928,7 +1049,13 @@
         <f>IF(A13="","",COUNTIF(招式表!$A$2:$A$201,A13))</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -941,7 +1068,13 @@
         <f>IF(A14="","",COUNTIF(招式表!$A$2:$A$201,A14))</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n"/>
@@ -954,7 +1087,13 @@
         <f>IF(A15="","",COUNTIF(招式表!$A$2:$A$201,A15))</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -967,7 +1106,13 @@
         <f>IF(A16="","",COUNTIF(招式表!$A$2:$A$201,A16))</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n"/>
@@ -980,7 +1125,13 @@
         <f>IF(A17="","",COUNTIF(招式表!$A$2:$A$201,A17))</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -993,7 +1144,13 @@
         <f>IF(A18="","",COUNTIF(招式表!$A$2:$A$201,A18))</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n"/>
@@ -1006,7 +1163,13 @@
         <f>IF(A19="","",COUNTIF(招式表!$A$2:$A$201,A19))</f>
         <v/>
       </c>
-      <c r="H19" s="14" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1019,7 +1182,13 @@
         <f>IF(A20="","",COUNTIF(招式表!$A$2:$A$201,A20))</f>
         <v/>
       </c>
-      <c r="H20" s="14" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
@@ -1032,7 +1201,13 @@
         <f>IF(A21="","",COUNTIF(招式表!$A$2:$A$201,A21))</f>
         <v/>
       </c>
-      <c r="H21" s="14" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1045,7 +1220,13 @@
         <f>IF(A22="","",COUNTIF(招式表!$A$2:$A$201,A22))</f>
         <v/>
       </c>
-      <c r="H22" s="14" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n"/>
@@ -1058,7 +1239,13 @@
         <f>IF(A23="","",COUNTIF(招式表!$A$2:$A$201,A23))</f>
         <v/>
       </c>
-      <c r="H23" s="14" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1071,7 +1258,13 @@
         <f>IF(A24="","",COUNTIF(招式表!$A$2:$A$201,A24))</f>
         <v/>
       </c>
-      <c r="H24" s="14" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n"/>
@@ -1084,7 +1277,13 @@
         <f>IF(A25="","",COUNTIF(招式表!$A$2:$A$201,A25))</f>
         <v/>
       </c>
-      <c r="H25" s="14" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1097,7 +1296,13 @@
         <f>IF(A26="","",COUNTIF(招式表!$A$2:$A$201,A26))</f>
         <v/>
       </c>
-      <c r="H26" s="14" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n"/>
@@ -1110,7 +1315,13 @@
         <f>IF(A27="","",COUNTIF(招式表!$A$2:$A$201,A27))</f>
         <v/>
       </c>
-      <c r="H27" s="14" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1123,7 +1334,13 @@
         <f>IF(A28="","",COUNTIF(招式表!$A$2:$A$201,A28))</f>
         <v/>
       </c>
-      <c r="H28" s="14" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n"/>
@@ -1136,7 +1353,13 @@
         <f>IF(A29="","",COUNTIF(招式表!$A$2:$A$201,A29))</f>
         <v/>
       </c>
-      <c r="H29" s="14" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1149,7 +1372,13 @@
         <f>IF(A30="","",COUNTIF(招式表!$A$2:$A$201,A30))</f>
         <v/>
       </c>
-      <c r="H30" s="14" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n"/>
@@ -1162,7 +1391,13 @@
         <f>IF(A31="","",COUNTIF(招式表!$A$2:$A$201,A31))</f>
         <v/>
       </c>
-      <c r="H31" s="14" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1175,7 +1410,13 @@
         <f>IF(A32="","",COUNTIF(招式表!$A$2:$A$201,A32))</f>
         <v/>
       </c>
-      <c r="H32" s="14" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n"/>
@@ -1188,7 +1429,13 @@
         <f>IF(A33="","",COUNTIF(招式表!$A$2:$A$201,A33))</f>
         <v/>
       </c>
-      <c r="H33" s="14" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1201,7 +1448,13 @@
         <f>IF(A34="","",COUNTIF(招式表!$A$2:$A$201,A34))</f>
         <v/>
       </c>
-      <c r="H34" s="14" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n"/>
@@ -1214,7 +1467,13 @@
         <f>IF(A35="","",COUNTIF(招式表!$A$2:$A$201,A35))</f>
         <v/>
       </c>
-      <c r="H35" s="14" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1227,7 +1486,13 @@
         <f>IF(A36="","",COUNTIF(招式表!$A$2:$A$201,A36))</f>
         <v/>
       </c>
-      <c r="H36" s="14" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n"/>
@@ -1240,7 +1505,13 @@
         <f>IF(A37="","",COUNTIF(招式表!$A$2:$A$201,A37))</f>
         <v/>
       </c>
-      <c r="H37" s="14" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1253,7 +1524,13 @@
         <f>IF(A38="","",COUNTIF(招式表!$A$2:$A$201,A38))</f>
         <v/>
       </c>
-      <c r="H38" s="14" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n"/>
@@ -1266,7 +1543,13 @@
         <f>IF(A39="","",COUNTIF(招式表!$A$2:$A$201,A39))</f>
         <v/>
       </c>
-      <c r="H39" s="14" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -1279,7 +1562,13 @@
         <f>IF(A40="","",COUNTIF(招式表!$A$2:$A$201,A40))</f>
         <v/>
       </c>
-      <c r="H40" s="14" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="12" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="12" t="n"/>
+      <c r="N40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n"/>
@@ -1292,7 +1581,13 @@
         <f>IF(A41="","",COUNTIF(招式表!$A$2:$A$201,A41))</f>
         <v/>
       </c>
-      <c r="H41" s="14" t="n"/>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="12" t="n"/>
+      <c r="N41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -1305,7 +1600,13 @@
         <f>IF(A42="","",COUNTIF(招式表!$A$2:$A$201,A42))</f>
         <v/>
       </c>
-      <c r="H42" s="14" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n"/>
@@ -1318,7 +1619,13 @@
         <f>IF(A43="","",COUNTIF(招式表!$A$2:$A$201,A43))</f>
         <v/>
       </c>
-      <c r="H43" s="14" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="12" t="n"/>
+      <c r="N43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -1331,7 +1638,13 @@
         <f>IF(A44="","",COUNTIF(招式表!$A$2:$A$201,A44))</f>
         <v/>
       </c>
-      <c r="H44" s="14" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="12" t="n"/>
+      <c r="N44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n"/>
@@ -1344,7 +1657,13 @@
         <f>IF(A45="","",COUNTIF(招式表!$A$2:$A$201,A45))</f>
         <v/>
       </c>
-      <c r="H45" s="14" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="12" t="n"/>
+      <c r="N45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -1357,7 +1676,13 @@
         <f>IF(A46="","",COUNTIF(招式表!$A$2:$A$201,A46))</f>
         <v/>
       </c>
-      <c r="H46" s="14" t="n"/>
+      <c r="H46" s="12" t="n"/>
+      <c r="I46" s="12" t="n"/>
+      <c r="J46" s="12" t="n"/>
+      <c r="K46" s="12" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="12" t="n"/>
+      <c r="N46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="n"/>
@@ -1370,7 +1695,13 @@
         <f>IF(A47="","",COUNTIF(招式表!$A$2:$A$201,A47))</f>
         <v/>
       </c>
-      <c r="H47" s="14" t="n"/>
+      <c r="H47" s="12" t="n"/>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="12" t="n"/>
+      <c r="N47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -1383,7 +1714,13 @@
         <f>IF(A48="","",COUNTIF(招式表!$A$2:$A$201,A48))</f>
         <v/>
       </c>
-      <c r="H48" s="14" t="n"/>
+      <c r="H48" s="12" t="n"/>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="12" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="12" t="n"/>
+      <c r="N48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n"/>
@@ -1396,7 +1733,13 @@
         <f>IF(A49="","",COUNTIF(招式表!$A$2:$A$201,A49))</f>
         <v/>
       </c>
-      <c r="H49" s="14" t="n"/>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="12" t="n"/>
+      <c r="N49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -1409,7 +1752,13 @@
         <f>IF(A50="","",COUNTIF(招式表!$A$2:$A$201,A50))</f>
         <v/>
       </c>
-      <c r="H50" s="14" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n"/>
@@ -1422,7 +1771,13 @@
         <f>IF(A51="","",COUNTIF(招式表!$A$2:$A$201,A51))</f>
         <v/>
       </c>
-      <c r="H51" s="14" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="12" t="n"/>
+      <c r="N51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -1435,7 +1790,13 @@
         <f>IF(A52="","",COUNTIF(招式表!$A$2:$A$201,A52))</f>
         <v/>
       </c>
-      <c r="H52" s="14" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="12" t="n"/>
+      <c r="N52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n"/>
@@ -1448,7 +1809,13 @@
         <f>IF(A53="","",COUNTIF(招式表!$A$2:$A$201,A53))</f>
         <v/>
       </c>
-      <c r="H53" s="14" t="n"/>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="12" t="n"/>
+      <c r="N53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -1461,7 +1828,13 @@
         <f>IF(A54="","",COUNTIF(招式表!$A$2:$A$201,A54))</f>
         <v/>
       </c>
-      <c r="H54" s="14" t="n"/>
+      <c r="H54" s="12" t="n"/>
+      <c r="I54" s="12" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="12" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="12" t="n"/>
+      <c r="N54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n"/>
@@ -1474,7 +1847,13 @@
         <f>IF(A55="","",COUNTIF(招式表!$A$2:$A$201,A55))</f>
         <v/>
       </c>
-      <c r="H55" s="14" t="n"/>
+      <c r="H55" s="12" t="n"/>
+      <c r="I55" s="12" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -1487,7 +1866,13 @@
         <f>IF(A56="","",COUNTIF(招式表!$A$2:$A$201,A56))</f>
         <v/>
       </c>
-      <c r="H56" s="14" t="n"/>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="12" t="n"/>
+      <c r="J56" s="12" t="n"/>
+      <c r="K56" s="12" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="12" t="n"/>
+      <c r="N56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n"/>
@@ -1500,7 +1885,13 @@
         <f>IF(A57="","",COUNTIF(招式表!$A$2:$A$201,A57))</f>
         <v/>
       </c>
-      <c r="H57" s="14" t="n"/>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="12" t="n"/>
+      <c r="N57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -1513,7 +1904,13 @@
         <f>IF(A58="","",COUNTIF(招式表!$A$2:$A$201,A58))</f>
         <v/>
       </c>
-      <c r="H58" s="14" t="n"/>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="12" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="12" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="12" t="n"/>
+      <c r="N58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n"/>
@@ -1526,7 +1923,13 @@
         <f>IF(A59="","",COUNTIF(招式表!$A$2:$A$201,A59))</f>
         <v/>
       </c>
-      <c r="H59" s="14" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="13" t="n"/>
+      <c r="M59" s="12" t="n"/>
+      <c r="N59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -1539,7 +1942,13 @@
         <f>IF(A60="","",COUNTIF(招式表!$A$2:$A$201,A60))</f>
         <v/>
       </c>
-      <c r="H60" s="14" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n"/>
@@ -1552,7 +1961,13 @@
         <f>IF(A61="","",COUNTIF(招式表!$A$2:$A$201,A61))</f>
         <v/>
       </c>
-      <c r="H61" s="14" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="13" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -1565,7 +1980,13 @@
         <f>IF(A62="","",COUNTIF(招式表!$A$2:$A$201,A62))</f>
         <v/>
       </c>
-      <c r="H62" s="14" t="n"/>
+      <c r="H62" s="12" t="n"/>
+      <c r="I62" s="12" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="12" t="n"/>
+      <c r="N62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n"/>
@@ -1578,7 +1999,13 @@
         <f>IF(A63="","",COUNTIF(招式表!$A$2:$A$201,A63))</f>
         <v/>
       </c>
-      <c r="H63" s="14" t="n"/>
+      <c r="H63" s="12" t="n"/>
+      <c r="I63" s="12" t="n"/>
+      <c r="J63" s="12" t="n"/>
+      <c r="K63" s="12" t="n"/>
+      <c r="L63" s="13" t="n"/>
+      <c r="M63" s="12" t="n"/>
+      <c r="N63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -1591,7 +2018,13 @@
         <f>IF(A64="","",COUNTIF(招式表!$A$2:$A$201,A64))</f>
         <v/>
       </c>
-      <c r="H64" s="14" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="n"/>
@@ -1604,7 +2037,13 @@
         <f>IF(A65="","",COUNTIF(招式表!$A$2:$A$201,A65))</f>
         <v/>
       </c>
-      <c r="H65" s="14" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="13" t="n"/>
+      <c r="M65" s="12" t="n"/>
+      <c r="N65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -1617,7 +2056,13 @@
         <f>IF(A66="","",COUNTIF(招式表!$A$2:$A$201,A66))</f>
         <v/>
       </c>
-      <c r="H66" s="14" t="n"/>
+      <c r="H66" s="12" t="n"/>
+      <c r="I66" s="12" t="n"/>
+      <c r="J66" s="12" t="n"/>
+      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="12" t="n"/>
+      <c r="N66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="n"/>
@@ -1630,7 +2075,13 @@
         <f>IF(A67="","",COUNTIF(招式表!$A$2:$A$201,A67))</f>
         <v/>
       </c>
-      <c r="H67" s="14" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="13" t="n"/>
+      <c r="M67" s="12" t="n"/>
+      <c r="N67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -1643,7 +2094,13 @@
         <f>IF(A68="","",COUNTIF(招式表!$A$2:$A$201,A68))</f>
         <v/>
       </c>
-      <c r="H68" s="14" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="12" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="12" t="n"/>
+      <c r="N68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="n"/>
@@ -1656,7 +2113,13 @@
         <f>IF(A69="","",COUNTIF(招式表!$A$2:$A$201,A69))</f>
         <v/>
       </c>
-      <c r="H69" s="14" t="n"/>
+      <c r="H69" s="12" t="n"/>
+      <c r="I69" s="12" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="13" t="n"/>
+      <c r="M69" s="12" t="n"/>
+      <c r="N69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -1669,7 +2132,13 @@
         <f>IF(A70="","",COUNTIF(招式表!$A$2:$A$201,A70))</f>
         <v/>
       </c>
-      <c r="H70" s="14" t="n"/>
+      <c r="H70" s="12" t="n"/>
+      <c r="I70" s="12" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="12" t="n"/>
+      <c r="N70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="n"/>
@@ -1682,7 +2151,13 @@
         <f>IF(A71="","",COUNTIF(招式表!$A$2:$A$201,A71))</f>
         <v/>
       </c>
-      <c r="H71" s="14" t="n"/>
+      <c r="H71" s="12" t="n"/>
+      <c r="I71" s="12" t="n"/>
+      <c r="J71" s="12" t="n"/>
+      <c r="K71" s="12" t="n"/>
+      <c r="L71" s="13" t="n"/>
+      <c r="M71" s="12" t="n"/>
+      <c r="N71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -1695,7 +2170,13 @@
         <f>IF(A72="","",COUNTIF(招式表!$A$2:$A$201,A72))</f>
         <v/>
       </c>
-      <c r="H72" s="14" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="12" t="n"/>
+      <c r="N72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n"/>
@@ -1708,7 +2189,13 @@
         <f>IF(A73="","",COUNTIF(招式表!$A$2:$A$201,A73))</f>
         <v/>
       </c>
-      <c r="H73" s="14" t="n"/>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="12" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="13" t="n"/>
+      <c r="M73" s="12" t="n"/>
+      <c r="N73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -1721,7 +2208,13 @@
         <f>IF(A74="","",COUNTIF(招式表!$A$2:$A$201,A74))</f>
         <v/>
       </c>
-      <c r="H74" s="14" t="n"/>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="12" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="12" t="n"/>
+      <c r="N74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n"/>
@@ -1734,7 +2227,13 @@
         <f>IF(A75="","",COUNTIF(招式表!$A$2:$A$201,A75))</f>
         <v/>
       </c>
-      <c r="H75" s="14" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="13" t="n"/>
+      <c r="M75" s="12" t="n"/>
+      <c r="N75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -1747,7 +2246,13 @@
         <f>IF(A76="","",COUNTIF(招式表!$A$2:$A$201,A76))</f>
         <v/>
       </c>
-      <c r="H76" s="14" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="12" t="n"/>
+      <c r="N76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n"/>
@@ -1760,7 +2265,13 @@
         <f>IF(A77="","",COUNTIF(招式表!$A$2:$A$201,A77))</f>
         <v/>
       </c>
-      <c r="H77" s="14" t="n"/>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="13" t="n"/>
+      <c r="M77" s="12" t="n"/>
+      <c r="N77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -1773,7 +2284,13 @@
         <f>IF(A78="","",COUNTIF(招式表!$A$2:$A$201,A78))</f>
         <v/>
       </c>
-      <c r="H78" s="14" t="n"/>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="12" t="n"/>
+      <c r="N78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n"/>
@@ -1786,7 +2303,13 @@
         <f>IF(A79="","",COUNTIF(招式表!$A$2:$A$201,A79))</f>
         <v/>
       </c>
-      <c r="H79" s="14" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="13" t="n"/>
+      <c r="M79" s="12" t="n"/>
+      <c r="N79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -1799,7 +2322,13 @@
         <f>IF(A80="","",COUNTIF(招式表!$A$2:$A$201,A80))</f>
         <v/>
       </c>
-      <c r="H80" s="14" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n"/>
@@ -1812,7 +2341,13 @@
         <f>IF(A81="","",COUNTIF(招式表!$A$2:$A$201,A81))</f>
         <v/>
       </c>
-      <c r="H81" s="14" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="13" t="n"/>
+      <c r="M81" s="12" t="n"/>
+      <c r="N81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -1825,7 +2360,13 @@
         <f>IF(A82="","",COUNTIF(招式表!$A$2:$A$201,A82))</f>
         <v/>
       </c>
-      <c r="H82" s="14" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="12" t="n"/>
+      <c r="N82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n"/>
@@ -1838,7 +2379,13 @@
         <f>IF(A83="","",COUNTIF(招式表!$A$2:$A$201,A83))</f>
         <v/>
       </c>
-      <c r="H83" s="14" t="n"/>
+      <c r="H83" s="12" t="n"/>
+      <c r="I83" s="12" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="13" t="n"/>
+      <c r="M83" s="12" t="n"/>
+      <c r="N83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -1851,7 +2398,13 @@
         <f>IF(A84="","",COUNTIF(招式表!$A$2:$A$201,A84))</f>
         <v/>
       </c>
-      <c r="H84" s="14" t="n"/>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="12" t="n"/>
+      <c r="N84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n"/>
@@ -1864,7 +2417,13 @@
         <f>IF(A85="","",COUNTIF(招式表!$A$2:$A$201,A85))</f>
         <v/>
       </c>
-      <c r="H85" s="14" t="n"/>
+      <c r="H85" s="12" t="n"/>
+      <c r="I85" s="12" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="13" t="n"/>
+      <c r="M85" s="12" t="n"/>
+      <c r="N85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -1877,7 +2436,13 @@
         <f>IF(A86="","",COUNTIF(招式表!$A$2:$A$201,A86))</f>
         <v/>
       </c>
-      <c r="H86" s="14" t="n"/>
+      <c r="H86" s="12" t="n"/>
+      <c r="I86" s="12" t="n"/>
+      <c r="J86" s="12" t="n"/>
+      <c r="K86" s="12" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="12" t="n"/>
+      <c r="N86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n"/>
@@ -1890,7 +2455,13 @@
         <f>IF(A87="","",COUNTIF(招式表!$A$2:$A$201,A87))</f>
         <v/>
       </c>
-      <c r="H87" s="14" t="n"/>
+      <c r="H87" s="12" t="n"/>
+      <c r="I87" s="12" t="n"/>
+      <c r="J87" s="12" t="n"/>
+      <c r="K87" s="12" t="n"/>
+      <c r="L87" s="13" t="n"/>
+      <c r="M87" s="12" t="n"/>
+      <c r="N87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -1903,7 +2474,13 @@
         <f>IF(A88="","",COUNTIF(招式表!$A$2:$A$201,A88))</f>
         <v/>
       </c>
-      <c r="H88" s="14" t="n"/>
+      <c r="H88" s="12" t="n"/>
+      <c r="I88" s="12" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="12" t="n"/>
+      <c r="N88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="n"/>
@@ -1916,7 +2493,13 @@
         <f>IF(A89="","",COUNTIF(招式表!$A$2:$A$201,A89))</f>
         <v/>
       </c>
-      <c r="H89" s="14" t="n"/>
+      <c r="H89" s="12" t="n"/>
+      <c r="I89" s="12" t="n"/>
+      <c r="J89" s="12" t="n"/>
+      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="13" t="n"/>
+      <c r="M89" s="12" t="n"/>
+      <c r="N89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -1929,7 +2512,13 @@
         <f>IF(A90="","",COUNTIF(招式表!$A$2:$A$201,A90))</f>
         <v/>
       </c>
-      <c r="H90" s="14" t="n"/>
+      <c r="H90" s="12" t="n"/>
+      <c r="I90" s="12" t="n"/>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="12" t="n"/>
+      <c r="N90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n"/>
@@ -1942,7 +2531,13 @@
         <f>IF(A91="","",COUNTIF(招式表!$A$2:$A$201,A91))</f>
         <v/>
       </c>
-      <c r="H91" s="14" t="n"/>
+      <c r="H91" s="12" t="n"/>
+      <c r="I91" s="12" t="n"/>
+      <c r="J91" s="12" t="n"/>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="13" t="n"/>
+      <c r="M91" s="12" t="n"/>
+      <c r="N91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -1955,7 +2550,13 @@
         <f>IF(A92="","",COUNTIF(招式表!$A$2:$A$201,A92))</f>
         <v/>
       </c>
-      <c r="H92" s="14" t="n"/>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="12" t="n"/>
+      <c r="N92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n"/>
@@ -1968,7 +2569,13 @@
         <f>IF(A93="","",COUNTIF(招式表!$A$2:$A$201,A93))</f>
         <v/>
       </c>
-      <c r="H93" s="14" t="n"/>
+      <c r="H93" s="12" t="n"/>
+      <c r="I93" s="12" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="13" t="n"/>
+      <c r="M93" s="12" t="n"/>
+      <c r="N93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -1981,7 +2588,13 @@
         <f>IF(A94="","",COUNTIF(招式表!$A$2:$A$201,A94))</f>
         <v/>
       </c>
-      <c r="H94" s="14" t="n"/>
+      <c r="H94" s="12" t="n"/>
+      <c r="I94" s="12" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="12" t="n"/>
+      <c r="N94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n"/>
@@ -1994,7 +2607,13 @@
         <f>IF(A95="","",COUNTIF(招式表!$A$2:$A$201,A95))</f>
         <v/>
       </c>
-      <c r="H95" s="14" t="n"/>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="13" t="n"/>
+      <c r="M95" s="12" t="n"/>
+      <c r="N95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -2007,7 +2626,13 @@
         <f>IF(A96="","",COUNTIF(招式表!$A$2:$A$201,A96))</f>
         <v/>
       </c>
-      <c r="H96" s="14" t="n"/>
+      <c r="H96" s="12" t="n"/>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="12" t="n"/>
+      <c r="N96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n"/>
@@ -2020,7 +2645,13 @@
         <f>IF(A97="","",COUNTIF(招式表!$A$2:$A$201,A97))</f>
         <v/>
       </c>
-      <c r="H97" s="14" t="n"/>
+      <c r="H97" s="12" t="n"/>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="13" t="n"/>
+      <c r="M97" s="12" t="n"/>
+      <c r="N97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -2033,7 +2664,13 @@
         <f>IF(A98="","",COUNTIF(招式表!$A$2:$A$201,A98))</f>
         <v/>
       </c>
-      <c r="H98" s="14" t="n"/>
+      <c r="H98" s="12" t="n"/>
+      <c r="I98" s="12" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="12" t="n"/>
+      <c r="N98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n"/>
@@ -2046,7 +2683,13 @@
         <f>IF(A99="","",COUNTIF(招式表!$A$2:$A$201,A99))</f>
         <v/>
       </c>
-      <c r="H99" s="14" t="n"/>
+      <c r="H99" s="12" t="n"/>
+      <c r="I99" s="12" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="13" t="n"/>
+      <c r="M99" s="12" t="n"/>
+      <c r="N99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -2059,7 +2702,13 @@
         <f>IF(A100="","",COUNTIF(招式表!$A$2:$A$201,A100))</f>
         <v/>
       </c>
-      <c r="H100" s="14" t="n"/>
+      <c r="H100" s="12" t="n"/>
+      <c r="I100" s="12" t="n"/>
+      <c r="J100" s="12" t="n"/>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="12" t="n"/>
+      <c r="N100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n"/>
@@ -2072,7 +2721,13 @@
         <f>IF(A101="","",COUNTIF(招式表!$A$2:$A$201,A101))</f>
         <v/>
       </c>
-      <c r="H101" s="14" t="n"/>
+      <c r="H101" s="12" t="n"/>
+      <c r="I101" s="12" t="n"/>
+      <c r="J101" s="12" t="n"/>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="13" t="n"/>
+      <c r="M101" s="12" t="n"/>
+      <c r="N101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -2085,7 +2740,13 @@
         <f>IF(A102="","",COUNTIF(招式表!$A$2:$A$201,A102))</f>
         <v/>
       </c>
-      <c r="H102" s="14" t="n"/>
+      <c r="H102" s="12" t="n"/>
+      <c r="I102" s="12" t="n"/>
+      <c r="J102" s="12" t="n"/>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="12" t="n"/>
+      <c r="N102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n"/>
@@ -2098,7 +2759,13 @@
         <f>IF(A103="","",COUNTIF(招式表!$A$2:$A$201,A103))</f>
         <v/>
       </c>
-      <c r="H103" s="14" t="n"/>
+      <c r="H103" s="12" t="n"/>
+      <c r="I103" s="12" t="n"/>
+      <c r="J103" s="12" t="n"/>
+      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="13" t="n"/>
+      <c r="M103" s="12" t="n"/>
+      <c r="N103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="n"/>
@@ -2111,7 +2778,13 @@
         <f>IF(A104="","",COUNTIF(招式表!$A$2:$A$201,A104))</f>
         <v/>
       </c>
-      <c r="H104" s="14" t="n"/>
+      <c r="H104" s="12" t="n"/>
+      <c r="I104" s="12" t="n"/>
+      <c r="J104" s="12" t="n"/>
+      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="13" t="n"/>
+      <c r="M104" s="12" t="n"/>
+      <c r="N104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n"/>
@@ -2124,7 +2797,13 @@
         <f>IF(A105="","",COUNTIF(招式表!$A$2:$A$201,A105))</f>
         <v/>
       </c>
-      <c r="H105" s="14" t="n"/>
+      <c r="H105" s="12" t="n"/>
+      <c r="I105" s="12" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="13" t="n"/>
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n"/>
@@ -2137,7 +2816,13 @@
         <f>IF(A106="","",COUNTIF(招式表!$A$2:$A$201,A106))</f>
         <v/>
       </c>
-      <c r="H106" s="14" t="n"/>
+      <c r="H106" s="12" t="n"/>
+      <c r="I106" s="12" t="n"/>
+      <c r="J106" s="12" t="n"/>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="13" t="n"/>
+      <c r="M106" s="12" t="n"/>
+      <c r="N106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n"/>
@@ -2150,7 +2835,13 @@
         <f>IF(A107="","",COUNTIF(招式表!$A$2:$A$201,A107))</f>
         <v/>
       </c>
-      <c r="H107" s="14" t="n"/>
+      <c r="H107" s="12" t="n"/>
+      <c r="I107" s="12" t="n"/>
+      <c r="J107" s="12" t="n"/>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="13" t="n"/>
+      <c r="M107" s="12" t="n"/>
+      <c r="N107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="n"/>
@@ -2163,7 +2854,13 @@
         <f>IF(A108="","",COUNTIF(招式表!$A$2:$A$201,A108))</f>
         <v/>
       </c>
-      <c r="H108" s="14" t="n"/>
+      <c r="H108" s="12" t="n"/>
+      <c r="I108" s="12" t="n"/>
+      <c r="J108" s="12" t="n"/>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="13" t="n"/>
+      <c r="M108" s="12" t="n"/>
+      <c r="N108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="n"/>
@@ -2176,7 +2873,13 @@
         <f>IF(A109="","",COUNTIF(招式表!$A$2:$A$201,A109))</f>
         <v/>
       </c>
-      <c r="H109" s="14" t="n"/>
+      <c r="H109" s="12" t="n"/>
+      <c r="I109" s="12" t="n"/>
+      <c r="J109" s="12" t="n"/>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="13" t="n"/>
+      <c r="M109" s="12" t="n"/>
+      <c r="N109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n"/>
@@ -2189,7 +2892,13 @@
         <f>IF(A110="","",COUNTIF(招式表!$A$2:$A$201,A110))</f>
         <v/>
       </c>
-      <c r="H110" s="14" t="n"/>
+      <c r="H110" s="12" t="n"/>
+      <c r="I110" s="12" t="n"/>
+      <c r="J110" s="12" t="n"/>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="13" t="n"/>
+      <c r="M110" s="12" t="n"/>
+      <c r="N110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n"/>
@@ -2202,7 +2911,13 @@
         <f>IF(A111="","",COUNTIF(招式表!$A$2:$A$201,A111))</f>
         <v/>
       </c>
-      <c r="H111" s="14" t="n"/>
+      <c r="H111" s="12" t="n"/>
+      <c r="I111" s="12" t="n"/>
+      <c r="J111" s="12" t="n"/>
+      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="13" t="n"/>
+      <c r="M111" s="12" t="n"/>
+      <c r="N111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n"/>
@@ -2215,7 +2930,13 @@
         <f>IF(A112="","",COUNTIF(招式表!$A$2:$A$201,A112))</f>
         <v/>
       </c>
-      <c r="H112" s="14" t="n"/>
+      <c r="H112" s="12" t="n"/>
+      <c r="I112" s="12" t="n"/>
+      <c r="J112" s="12" t="n"/>
+      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="13" t="n"/>
+      <c r="M112" s="12" t="n"/>
+      <c r="N112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="n"/>
@@ -2228,7 +2949,13 @@
         <f>IF(A113="","",COUNTIF(招式表!$A$2:$A$201,A113))</f>
         <v/>
       </c>
-      <c r="H113" s="14" t="n"/>
+      <c r="H113" s="12" t="n"/>
+      <c r="I113" s="12" t="n"/>
+      <c r="J113" s="12" t="n"/>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="13" t="n"/>
+      <c r="M113" s="12" t="n"/>
+      <c r="N113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n"/>
@@ -2241,7 +2968,13 @@
         <f>IF(A114="","",COUNTIF(招式表!$A$2:$A$201,A114))</f>
         <v/>
       </c>
-      <c r="H114" s="14" t="n"/>
+      <c r="H114" s="12" t="n"/>
+      <c r="I114" s="12" t="n"/>
+      <c r="J114" s="12" t="n"/>
+      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="13" t="n"/>
+      <c r="M114" s="12" t="n"/>
+      <c r="N114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n"/>
@@ -2254,7 +2987,13 @@
         <f>IF(A115="","",COUNTIF(招式表!$A$2:$A$201,A115))</f>
         <v/>
       </c>
-      <c r="H115" s="14" t="n"/>
+      <c r="H115" s="12" t="n"/>
+      <c r="I115" s="12" t="n"/>
+      <c r="J115" s="12" t="n"/>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="13" t="n"/>
+      <c r="M115" s="12" t="n"/>
+      <c r="N115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n"/>
@@ -2267,7 +3006,13 @@
         <f>IF(A116="","",COUNTIF(招式表!$A$2:$A$201,A116))</f>
         <v/>
       </c>
-      <c r="H116" s="14" t="n"/>
+      <c r="H116" s="12" t="n"/>
+      <c r="I116" s="12" t="n"/>
+      <c r="J116" s="12" t="n"/>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="13" t="n"/>
+      <c r="M116" s="12" t="n"/>
+      <c r="N116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n"/>
@@ -2280,7 +3025,13 @@
         <f>IF(A117="","",COUNTIF(招式表!$A$2:$A$201,A117))</f>
         <v/>
       </c>
-      <c r="H117" s="14" t="n"/>
+      <c r="H117" s="12" t="n"/>
+      <c r="I117" s="12" t="n"/>
+      <c r="J117" s="12" t="n"/>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="13" t="n"/>
+      <c r="M117" s="12" t="n"/>
+      <c r="N117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n"/>
@@ -2293,7 +3044,13 @@
         <f>IF(A118="","",COUNTIF(招式表!$A$2:$A$201,A118))</f>
         <v/>
       </c>
-      <c r="H118" s="14" t="n"/>
+      <c r="H118" s="12" t="n"/>
+      <c r="I118" s="12" t="n"/>
+      <c r="J118" s="12" t="n"/>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="13" t="n"/>
+      <c r="M118" s="12" t="n"/>
+      <c r="N118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n"/>
@@ -2306,7 +3063,13 @@
         <f>IF(A119="","",COUNTIF(招式表!$A$2:$A$201,A119))</f>
         <v/>
       </c>
-      <c r="H119" s="14" t="n"/>
+      <c r="H119" s="12" t="n"/>
+      <c r="I119" s="12" t="n"/>
+      <c r="J119" s="12" t="n"/>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="13" t="n"/>
+      <c r="M119" s="12" t="n"/>
+      <c r="N119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n"/>
@@ -2319,7 +3082,13 @@
         <f>IF(A120="","",COUNTIF(招式表!$A$2:$A$201,A120))</f>
         <v/>
       </c>
-      <c r="H120" s="14" t="n"/>
+      <c r="H120" s="12" t="n"/>
+      <c r="I120" s="12" t="n"/>
+      <c r="J120" s="12" t="n"/>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="13" t="n"/>
+      <c r="M120" s="12" t="n"/>
+      <c r="N120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n"/>
@@ -2332,7 +3101,13 @@
         <f>IF(A121="","",COUNTIF(招式表!$A$2:$A$201,A121))</f>
         <v/>
       </c>
-      <c r="H121" s="14" t="n"/>
+      <c r="H121" s="12" t="n"/>
+      <c r="I121" s="12" t="n"/>
+      <c r="J121" s="12" t="n"/>
+      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="13" t="n"/>
+      <c r="M121" s="12" t="n"/>
+      <c r="N121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n"/>
@@ -2345,7 +3120,13 @@
         <f>IF(A122="","",COUNTIF(招式表!$A$2:$A$201,A122))</f>
         <v/>
       </c>
-      <c r="H122" s="14" t="n"/>
+      <c r="H122" s="12" t="n"/>
+      <c r="I122" s="12" t="n"/>
+      <c r="J122" s="12" t="n"/>
+      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="13" t="n"/>
+      <c r="M122" s="12" t="n"/>
+      <c r="N122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n"/>
@@ -2358,7 +3139,13 @@
         <f>IF(A123="","",COUNTIF(招式表!$A$2:$A$201,A123))</f>
         <v/>
       </c>
-      <c r="H123" s="14" t="n"/>
+      <c r="H123" s="12" t="n"/>
+      <c r="I123" s="12" t="n"/>
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="13" t="n"/>
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n"/>
@@ -2371,7 +3158,13 @@
         <f>IF(A124="","",COUNTIF(招式表!$A$2:$A$201,A124))</f>
         <v/>
       </c>
-      <c r="H124" s="14" t="n"/>
+      <c r="H124" s="12" t="n"/>
+      <c r="I124" s="12" t="n"/>
+      <c r="J124" s="12" t="n"/>
+      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="13" t="n"/>
+      <c r="M124" s="12" t="n"/>
+      <c r="N124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="n"/>
@@ -2384,7 +3177,13 @@
         <f>IF(A125="","",COUNTIF(招式表!$A$2:$A$201,A125))</f>
         <v/>
       </c>
-      <c r="H125" s="14" t="n"/>
+      <c r="H125" s="12" t="n"/>
+      <c r="I125" s="12" t="n"/>
+      <c r="J125" s="12" t="n"/>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="13" t="n"/>
+      <c r="M125" s="12" t="n"/>
+      <c r="N125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n"/>
@@ -2397,7 +3196,13 @@
         <f>IF(A126="","",COUNTIF(招式表!$A$2:$A$201,A126))</f>
         <v/>
       </c>
-      <c r="H126" s="14" t="n"/>
+      <c r="H126" s="12" t="n"/>
+      <c r="I126" s="12" t="n"/>
+      <c r="J126" s="12" t="n"/>
+      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="13" t="n"/>
+      <c r="M126" s="12" t="n"/>
+      <c r="N126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n"/>
@@ -2410,7 +3215,13 @@
         <f>IF(A127="","",COUNTIF(招式表!$A$2:$A$201,A127))</f>
         <v/>
       </c>
-      <c r="H127" s="14" t="n"/>
+      <c r="H127" s="12" t="n"/>
+      <c r="I127" s="12" t="n"/>
+      <c r="J127" s="12" t="n"/>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="13" t="n"/>
+      <c r="M127" s="12" t="n"/>
+      <c r="N127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n"/>
@@ -2423,7 +3234,13 @@
         <f>IF(A128="","",COUNTIF(招式表!$A$2:$A$201,A128))</f>
         <v/>
       </c>
-      <c r="H128" s="14" t="n"/>
+      <c r="H128" s="12" t="n"/>
+      <c r="I128" s="12" t="n"/>
+      <c r="J128" s="12" t="n"/>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="13" t="n"/>
+      <c r="M128" s="12" t="n"/>
+      <c r="N128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n"/>
@@ -2436,7 +3253,13 @@
         <f>IF(A129="","",COUNTIF(招式表!$A$2:$A$201,A129))</f>
         <v/>
       </c>
-      <c r="H129" s="14" t="n"/>
+      <c r="H129" s="12" t="n"/>
+      <c r="I129" s="12" t="n"/>
+      <c r="J129" s="12" t="n"/>
+      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="13" t="n"/>
+      <c r="M129" s="12" t="n"/>
+      <c r="N129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n"/>
@@ -2449,7 +3272,13 @@
         <f>IF(A130="","",COUNTIF(招式表!$A$2:$A$201,A130))</f>
         <v/>
       </c>
-      <c r="H130" s="14" t="n"/>
+      <c r="H130" s="12" t="n"/>
+      <c r="I130" s="12" t="n"/>
+      <c r="J130" s="12" t="n"/>
+      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="13" t="n"/>
+      <c r="M130" s="12" t="n"/>
+      <c r="N130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n"/>
@@ -2462,7 +3291,13 @@
         <f>IF(A131="","",COUNTIF(招式表!$A$2:$A$201,A131))</f>
         <v/>
       </c>
-      <c r="H131" s="14" t="n"/>
+      <c r="H131" s="12" t="n"/>
+      <c r="I131" s="12" t="n"/>
+      <c r="J131" s="12" t="n"/>
+      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="13" t="n"/>
+      <c r="M131" s="12" t="n"/>
+      <c r="N131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n"/>
@@ -2475,7 +3310,13 @@
         <f>IF(A132="","",COUNTIF(招式表!$A$2:$A$201,A132))</f>
         <v/>
       </c>
-      <c r="H132" s="14" t="n"/>
+      <c r="H132" s="12" t="n"/>
+      <c r="I132" s="12" t="n"/>
+      <c r="J132" s="12" t="n"/>
+      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="13" t="n"/>
+      <c r="M132" s="12" t="n"/>
+      <c r="N132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n"/>
@@ -2488,7 +3329,13 @@
         <f>IF(A133="","",COUNTIF(招式表!$A$2:$A$201,A133))</f>
         <v/>
       </c>
-      <c r="H133" s="14" t="n"/>
+      <c r="H133" s="12" t="n"/>
+      <c r="I133" s="12" t="n"/>
+      <c r="J133" s="12" t="n"/>
+      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="13" t="n"/>
+      <c r="M133" s="12" t="n"/>
+      <c r="N133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n"/>
@@ -2501,7 +3348,13 @@
         <f>IF(A134="","",COUNTIF(招式表!$A$2:$A$201,A134))</f>
         <v/>
       </c>
-      <c r="H134" s="14" t="n"/>
+      <c r="H134" s="12" t="n"/>
+      <c r="I134" s="12" t="n"/>
+      <c r="J134" s="12" t="n"/>
+      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="13" t="n"/>
+      <c r="M134" s="12" t="n"/>
+      <c r="N134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n"/>
@@ -2514,7 +3367,13 @@
         <f>IF(A135="","",COUNTIF(招式表!$A$2:$A$201,A135))</f>
         <v/>
       </c>
-      <c r="H135" s="14" t="n"/>
+      <c r="H135" s="12" t="n"/>
+      <c r="I135" s="12" t="n"/>
+      <c r="J135" s="12" t="n"/>
+      <c r="K135" s="12" t="n"/>
+      <c r="L135" s="13" t="n"/>
+      <c r="M135" s="12" t="n"/>
+      <c r="N135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n"/>
@@ -2527,7 +3386,13 @@
         <f>IF(A136="","",COUNTIF(招式表!$A$2:$A$201,A136))</f>
         <v/>
       </c>
-      <c r="H136" s="14" t="n"/>
+      <c r="H136" s="12" t="n"/>
+      <c r="I136" s="12" t="n"/>
+      <c r="J136" s="12" t="n"/>
+      <c r="K136" s="12" t="n"/>
+      <c r="L136" s="13" t="n"/>
+      <c r="M136" s="12" t="n"/>
+      <c r="N136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="n"/>
@@ -2540,7 +3405,13 @@
         <f>IF(A137="","",COUNTIF(招式表!$A$2:$A$201,A137))</f>
         <v/>
       </c>
-      <c r="H137" s="14" t="n"/>
+      <c r="H137" s="12" t="n"/>
+      <c r="I137" s="12" t="n"/>
+      <c r="J137" s="12" t="n"/>
+      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="13" t="n"/>
+      <c r="M137" s="12" t="n"/>
+      <c r="N137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="n"/>
@@ -2553,7 +3424,13 @@
         <f>IF(A138="","",COUNTIF(招式表!$A$2:$A$201,A138))</f>
         <v/>
       </c>
-      <c r="H138" s="14" t="n"/>
+      <c r="H138" s="12" t="n"/>
+      <c r="I138" s="12" t="n"/>
+      <c r="J138" s="12" t="n"/>
+      <c r="K138" s="12" t="n"/>
+      <c r="L138" s="13" t="n"/>
+      <c r="M138" s="12" t="n"/>
+      <c r="N138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="n"/>
@@ -2566,7 +3443,13 @@
         <f>IF(A139="","",COUNTIF(招式表!$A$2:$A$201,A139))</f>
         <v/>
       </c>
-      <c r="H139" s="14" t="n"/>
+      <c r="H139" s="12" t="n"/>
+      <c r="I139" s="12" t="n"/>
+      <c r="J139" s="12" t="n"/>
+      <c r="K139" s="12" t="n"/>
+      <c r="L139" s="13" t="n"/>
+      <c r="M139" s="12" t="n"/>
+      <c r="N139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="n"/>
@@ -2579,7 +3462,13 @@
         <f>IF(A140="","",COUNTIF(招式表!$A$2:$A$201,A140))</f>
         <v/>
       </c>
-      <c r="H140" s="14" t="n"/>
+      <c r="H140" s="12" t="n"/>
+      <c r="I140" s="12" t="n"/>
+      <c r="J140" s="12" t="n"/>
+      <c r="K140" s="12" t="n"/>
+      <c r="L140" s="13" t="n"/>
+      <c r="M140" s="12" t="n"/>
+      <c r="N140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="n"/>
@@ -2592,7 +3481,13 @@
         <f>IF(A141="","",COUNTIF(招式表!$A$2:$A$201,A141))</f>
         <v/>
       </c>
-      <c r="H141" s="14" t="n"/>
+      <c r="H141" s="12" t="n"/>
+      <c r="I141" s="12" t="n"/>
+      <c r="J141" s="12" t="n"/>
+      <c r="K141" s="12" t="n"/>
+      <c r="L141" s="13" t="n"/>
+      <c r="M141" s="12" t="n"/>
+      <c r="N141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="n"/>
@@ -2605,7 +3500,13 @@
         <f>IF(A142="","",COUNTIF(招式表!$A$2:$A$201,A142))</f>
         <v/>
       </c>
-      <c r="H142" s="14" t="n"/>
+      <c r="H142" s="12" t="n"/>
+      <c r="I142" s="12" t="n"/>
+      <c r="J142" s="12" t="n"/>
+      <c r="K142" s="12" t="n"/>
+      <c r="L142" s="13" t="n"/>
+      <c r="M142" s="12" t="n"/>
+      <c r="N142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="n"/>
@@ -2618,7 +3519,13 @@
         <f>IF(A143="","",COUNTIF(招式表!$A$2:$A$201,A143))</f>
         <v/>
       </c>
-      <c r="H143" s="14" t="n"/>
+      <c r="H143" s="12" t="n"/>
+      <c r="I143" s="12" t="n"/>
+      <c r="J143" s="12" t="n"/>
+      <c r="K143" s="12" t="n"/>
+      <c r="L143" s="13" t="n"/>
+      <c r="M143" s="12" t="n"/>
+      <c r="N143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="n"/>
@@ -2631,7 +3538,13 @@
         <f>IF(A144="","",COUNTIF(招式表!$A$2:$A$201,A144))</f>
         <v/>
       </c>
-      <c r="H144" s="14" t="n"/>
+      <c r="H144" s="12" t="n"/>
+      <c r="I144" s="12" t="n"/>
+      <c r="J144" s="12" t="n"/>
+      <c r="K144" s="12" t="n"/>
+      <c r="L144" s="13" t="n"/>
+      <c r="M144" s="12" t="n"/>
+      <c r="N144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="n"/>
@@ -2644,7 +3557,13 @@
         <f>IF(A145="","",COUNTIF(招式表!$A$2:$A$201,A145))</f>
         <v/>
       </c>
-      <c r="H145" s="14" t="n"/>
+      <c r="H145" s="12" t="n"/>
+      <c r="I145" s="12" t="n"/>
+      <c r="J145" s="12" t="n"/>
+      <c r="K145" s="12" t="n"/>
+      <c r="L145" s="13" t="n"/>
+      <c r="M145" s="12" t="n"/>
+      <c r="N145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="n"/>
@@ -2657,7 +3576,13 @@
         <f>IF(A146="","",COUNTIF(招式表!$A$2:$A$201,A146))</f>
         <v/>
       </c>
-      <c r="H146" s="14" t="n"/>
+      <c r="H146" s="12" t="n"/>
+      <c r="I146" s="12" t="n"/>
+      <c r="J146" s="12" t="n"/>
+      <c r="K146" s="12" t="n"/>
+      <c r="L146" s="13" t="n"/>
+      <c r="M146" s="12" t="n"/>
+      <c r="N146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="n"/>
@@ -2670,7 +3595,13 @@
         <f>IF(A147="","",COUNTIF(招式表!$A$2:$A$201,A147))</f>
         <v/>
       </c>
-      <c r="H147" s="14" t="n"/>
+      <c r="H147" s="12" t="n"/>
+      <c r="I147" s="12" t="n"/>
+      <c r="J147" s="12" t="n"/>
+      <c r="K147" s="12" t="n"/>
+      <c r="L147" s="13" t="n"/>
+      <c r="M147" s="12" t="n"/>
+      <c r="N147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="n"/>
@@ -2683,7 +3614,13 @@
         <f>IF(A148="","",COUNTIF(招式表!$A$2:$A$201,A148))</f>
         <v/>
       </c>
-      <c r="H148" s="14" t="n"/>
+      <c r="H148" s="12" t="n"/>
+      <c r="I148" s="12" t="n"/>
+      <c r="J148" s="12" t="n"/>
+      <c r="K148" s="12" t="n"/>
+      <c r="L148" s="13" t="n"/>
+      <c r="M148" s="12" t="n"/>
+      <c r="N148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="n"/>
@@ -2696,7 +3633,13 @@
         <f>IF(A149="","",COUNTIF(招式表!$A$2:$A$201,A149))</f>
         <v/>
       </c>
-      <c r="H149" s="14" t="n"/>
+      <c r="H149" s="12" t="n"/>
+      <c r="I149" s="12" t="n"/>
+      <c r="J149" s="12" t="n"/>
+      <c r="K149" s="12" t="n"/>
+      <c r="L149" s="13" t="n"/>
+      <c r="M149" s="12" t="n"/>
+      <c r="N149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="n"/>
@@ -2709,7 +3652,13 @@
         <f>IF(A150="","",COUNTIF(招式表!$A$2:$A$201,A150))</f>
         <v/>
       </c>
-      <c r="H150" s="14" t="n"/>
+      <c r="H150" s="12" t="n"/>
+      <c r="I150" s="12" t="n"/>
+      <c r="J150" s="12" t="n"/>
+      <c r="K150" s="12" t="n"/>
+      <c r="L150" s="13" t="n"/>
+      <c r="M150" s="12" t="n"/>
+      <c r="N150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="n"/>
@@ -2722,7 +3671,13 @@
         <f>IF(A151="","",COUNTIF(招式表!$A$2:$A$201,A151))</f>
         <v/>
       </c>
-      <c r="H151" s="14" t="n"/>
+      <c r="H151" s="12" t="n"/>
+      <c r="I151" s="12" t="n"/>
+      <c r="J151" s="12" t="n"/>
+      <c r="K151" s="12" t="n"/>
+      <c r="L151" s="13" t="n"/>
+      <c r="M151" s="12" t="n"/>
+      <c r="N151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="n"/>
@@ -2735,7 +3690,13 @@
         <f>IF(A152="","",COUNTIF(招式表!$A$2:$A$201,A152))</f>
         <v/>
       </c>
-      <c r="H152" s="14" t="n"/>
+      <c r="H152" s="12" t="n"/>
+      <c r="I152" s="12" t="n"/>
+      <c r="J152" s="12" t="n"/>
+      <c r="K152" s="12" t="n"/>
+      <c r="L152" s="13" t="n"/>
+      <c r="M152" s="12" t="n"/>
+      <c r="N152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="n"/>
@@ -2748,7 +3709,13 @@
         <f>IF(A153="","",COUNTIF(招式表!$A$2:$A$201,A153))</f>
         <v/>
       </c>
-      <c r="H153" s="14" t="n"/>
+      <c r="H153" s="12" t="n"/>
+      <c r="I153" s="12" t="n"/>
+      <c r="J153" s="12" t="n"/>
+      <c r="K153" s="12" t="n"/>
+      <c r="L153" s="13" t="n"/>
+      <c r="M153" s="12" t="n"/>
+      <c r="N153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="n"/>
@@ -2761,7 +3728,13 @@
         <f>IF(A154="","",COUNTIF(招式表!$A$2:$A$201,A154))</f>
         <v/>
       </c>
-      <c r="H154" s="14" t="n"/>
+      <c r="H154" s="12" t="n"/>
+      <c r="I154" s="12" t="n"/>
+      <c r="J154" s="12" t="n"/>
+      <c r="K154" s="12" t="n"/>
+      <c r="L154" s="13" t="n"/>
+      <c r="M154" s="12" t="n"/>
+      <c r="N154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n"/>
@@ -2774,7 +3747,13 @@
         <f>IF(A155="","",COUNTIF(招式表!$A$2:$A$201,A155))</f>
         <v/>
       </c>
-      <c r="H155" s="14" t="n"/>
+      <c r="H155" s="12" t="n"/>
+      <c r="I155" s="12" t="n"/>
+      <c r="J155" s="12" t="n"/>
+      <c r="K155" s="12" t="n"/>
+      <c r="L155" s="13" t="n"/>
+      <c r="M155" s="12" t="n"/>
+      <c r="N155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="n"/>
@@ -2787,7 +3766,13 @@
         <f>IF(A156="","",COUNTIF(招式表!$A$2:$A$201,A156))</f>
         <v/>
       </c>
-      <c r="H156" s="14" t="n"/>
+      <c r="H156" s="12" t="n"/>
+      <c r="I156" s="12" t="n"/>
+      <c r="J156" s="12" t="n"/>
+      <c r="K156" s="12" t="n"/>
+      <c r="L156" s="13" t="n"/>
+      <c r="M156" s="12" t="n"/>
+      <c r="N156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="n"/>
@@ -2800,7 +3785,13 @@
         <f>IF(A157="","",COUNTIF(招式表!$A$2:$A$201,A157))</f>
         <v/>
       </c>
-      <c r="H157" s="14" t="n"/>
+      <c r="H157" s="12" t="n"/>
+      <c r="I157" s="12" t="n"/>
+      <c r="J157" s="12" t="n"/>
+      <c r="K157" s="12" t="n"/>
+      <c r="L157" s="13" t="n"/>
+      <c r="M157" s="12" t="n"/>
+      <c r="N157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="n"/>
@@ -2813,7 +3804,13 @@
         <f>IF(A158="","",COUNTIF(招式表!$A$2:$A$201,A158))</f>
         <v/>
       </c>
-      <c r="H158" s="14" t="n"/>
+      <c r="H158" s="12" t="n"/>
+      <c r="I158" s="12" t="n"/>
+      <c r="J158" s="12" t="n"/>
+      <c r="K158" s="12" t="n"/>
+      <c r="L158" s="13" t="n"/>
+      <c r="M158" s="12" t="n"/>
+      <c r="N158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="n"/>
@@ -2826,7 +3823,13 @@
         <f>IF(A159="","",COUNTIF(招式表!$A$2:$A$201,A159))</f>
         <v/>
       </c>
-      <c r="H159" s="14" t="n"/>
+      <c r="H159" s="12" t="n"/>
+      <c r="I159" s="12" t="n"/>
+      <c r="J159" s="12" t="n"/>
+      <c r="K159" s="12" t="n"/>
+      <c r="L159" s="13" t="n"/>
+      <c r="M159" s="12" t="n"/>
+      <c r="N159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="n"/>
@@ -2839,7 +3842,13 @@
         <f>IF(A160="","",COUNTIF(招式表!$A$2:$A$201,A160))</f>
         <v/>
       </c>
-      <c r="H160" s="14" t="n"/>
+      <c r="H160" s="12" t="n"/>
+      <c r="I160" s="12" t="n"/>
+      <c r="J160" s="12" t="n"/>
+      <c r="K160" s="12" t="n"/>
+      <c r="L160" s="13" t="n"/>
+      <c r="M160" s="12" t="n"/>
+      <c r="N160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="n"/>
@@ -2852,7 +3861,13 @@
         <f>IF(A161="","",COUNTIF(招式表!$A$2:$A$201,A161))</f>
         <v/>
       </c>
-      <c r="H161" s="14" t="n"/>
+      <c r="H161" s="12" t="n"/>
+      <c r="I161" s="12" t="n"/>
+      <c r="J161" s="12" t="n"/>
+      <c r="K161" s="12" t="n"/>
+      <c r="L161" s="13" t="n"/>
+      <c r="M161" s="12" t="n"/>
+      <c r="N161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="n"/>
@@ -2865,7 +3880,13 @@
         <f>IF(A162="","",COUNTIF(招式表!$A$2:$A$201,A162))</f>
         <v/>
       </c>
-      <c r="H162" s="14" t="n"/>
+      <c r="H162" s="12" t="n"/>
+      <c r="I162" s="12" t="n"/>
+      <c r="J162" s="12" t="n"/>
+      <c r="K162" s="12" t="n"/>
+      <c r="L162" s="13" t="n"/>
+      <c r="M162" s="12" t="n"/>
+      <c r="N162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="n"/>
@@ -2878,7 +3899,13 @@
         <f>IF(A163="","",COUNTIF(招式表!$A$2:$A$201,A163))</f>
         <v/>
       </c>
-      <c r="H163" s="14" t="n"/>
+      <c r="H163" s="12" t="n"/>
+      <c r="I163" s="12" t="n"/>
+      <c r="J163" s="12" t="n"/>
+      <c r="K163" s="12" t="n"/>
+      <c r="L163" s="13" t="n"/>
+      <c r="M163" s="12" t="n"/>
+      <c r="N163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="n"/>
@@ -2891,7 +3918,13 @@
         <f>IF(A164="","",COUNTIF(招式表!$A$2:$A$201,A164))</f>
         <v/>
       </c>
-      <c r="H164" s="14" t="n"/>
+      <c r="H164" s="12" t="n"/>
+      <c r="I164" s="12" t="n"/>
+      <c r="J164" s="12" t="n"/>
+      <c r="K164" s="12" t="n"/>
+      <c r="L164" s="13" t="n"/>
+      <c r="M164" s="12" t="n"/>
+      <c r="N164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="n"/>
@@ -2904,7 +3937,13 @@
         <f>IF(A165="","",COUNTIF(招式表!$A$2:$A$201,A165))</f>
         <v/>
       </c>
-      <c r="H165" s="14" t="n"/>
+      <c r="H165" s="12" t="n"/>
+      <c r="I165" s="12" t="n"/>
+      <c r="J165" s="12" t="n"/>
+      <c r="K165" s="12" t="n"/>
+      <c r="L165" s="13" t="n"/>
+      <c r="M165" s="12" t="n"/>
+      <c r="N165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="n"/>
@@ -2917,7 +3956,13 @@
         <f>IF(A166="","",COUNTIF(招式表!$A$2:$A$201,A166))</f>
         <v/>
       </c>
-      <c r="H166" s="14" t="n"/>
+      <c r="H166" s="12" t="n"/>
+      <c r="I166" s="12" t="n"/>
+      <c r="J166" s="12" t="n"/>
+      <c r="K166" s="12" t="n"/>
+      <c r="L166" s="13" t="n"/>
+      <c r="M166" s="12" t="n"/>
+      <c r="N166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="n"/>
@@ -2930,7 +3975,13 @@
         <f>IF(A167="","",COUNTIF(招式表!$A$2:$A$201,A167))</f>
         <v/>
       </c>
-      <c r="H167" s="14" t="n"/>
+      <c r="H167" s="12" t="n"/>
+      <c r="I167" s="12" t="n"/>
+      <c r="J167" s="12" t="n"/>
+      <c r="K167" s="12" t="n"/>
+      <c r="L167" s="13" t="n"/>
+      <c r="M167" s="12" t="n"/>
+      <c r="N167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="n"/>
@@ -2943,7 +3994,13 @@
         <f>IF(A168="","",COUNTIF(招式表!$A$2:$A$201,A168))</f>
         <v/>
       </c>
-      <c r="H168" s="14" t="n"/>
+      <c r="H168" s="12" t="n"/>
+      <c r="I168" s="12" t="n"/>
+      <c r="J168" s="12" t="n"/>
+      <c r="K168" s="12" t="n"/>
+      <c r="L168" s="13" t="n"/>
+      <c r="M168" s="12" t="n"/>
+      <c r="N168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="n"/>
@@ -2956,7 +4013,13 @@
         <f>IF(A169="","",COUNTIF(招式表!$A$2:$A$201,A169))</f>
         <v/>
       </c>
-      <c r="H169" s="14" t="n"/>
+      <c r="H169" s="12" t="n"/>
+      <c r="I169" s="12" t="n"/>
+      <c r="J169" s="12" t="n"/>
+      <c r="K169" s="12" t="n"/>
+      <c r="L169" s="13" t="n"/>
+      <c r="M169" s="12" t="n"/>
+      <c r="N169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="n"/>
@@ -2969,7 +4032,13 @@
         <f>IF(A170="","",COUNTIF(招式表!$A$2:$A$201,A170))</f>
         <v/>
       </c>
-      <c r="H170" s="14" t="n"/>
+      <c r="H170" s="12" t="n"/>
+      <c r="I170" s="12" t="n"/>
+      <c r="J170" s="12" t="n"/>
+      <c r="K170" s="12" t="n"/>
+      <c r="L170" s="13" t="n"/>
+      <c r="M170" s="12" t="n"/>
+      <c r="N170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="n"/>
@@ -2982,7 +4051,13 @@
         <f>IF(A171="","",COUNTIF(招式表!$A$2:$A$201,A171))</f>
         <v/>
       </c>
-      <c r="H171" s="14" t="n"/>
+      <c r="H171" s="12" t="n"/>
+      <c r="I171" s="12" t="n"/>
+      <c r="J171" s="12" t="n"/>
+      <c r="K171" s="12" t="n"/>
+      <c r="L171" s="13" t="n"/>
+      <c r="M171" s="12" t="n"/>
+      <c r="N171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="n"/>
@@ -2995,7 +4070,13 @@
         <f>IF(A172="","",COUNTIF(招式表!$A$2:$A$201,A172))</f>
         <v/>
       </c>
-      <c r="H172" s="14" t="n"/>
+      <c r="H172" s="12" t="n"/>
+      <c r="I172" s="12" t="n"/>
+      <c r="J172" s="12" t="n"/>
+      <c r="K172" s="12" t="n"/>
+      <c r="L172" s="13" t="n"/>
+      <c r="M172" s="12" t="n"/>
+      <c r="N172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="n"/>
@@ -3008,7 +4089,13 @@
         <f>IF(A173="","",COUNTIF(招式表!$A$2:$A$201,A173))</f>
         <v/>
       </c>
-      <c r="H173" s="14" t="n"/>
+      <c r="H173" s="12" t="n"/>
+      <c r="I173" s="12" t="n"/>
+      <c r="J173" s="12" t="n"/>
+      <c r="K173" s="12" t="n"/>
+      <c r="L173" s="13" t="n"/>
+      <c r="M173" s="12" t="n"/>
+      <c r="N173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="n"/>
@@ -3021,7 +4108,13 @@
         <f>IF(A174="","",COUNTIF(招式表!$A$2:$A$201,A174))</f>
         <v/>
       </c>
-      <c r="H174" s="14" t="n"/>
+      <c r="H174" s="12" t="n"/>
+      <c r="I174" s="12" t="n"/>
+      <c r="J174" s="12" t="n"/>
+      <c r="K174" s="12" t="n"/>
+      <c r="L174" s="13" t="n"/>
+      <c r="M174" s="12" t="n"/>
+      <c r="N174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="n"/>
@@ -3034,7 +4127,13 @@
         <f>IF(A175="","",COUNTIF(招式表!$A$2:$A$201,A175))</f>
         <v/>
       </c>
-      <c r="H175" s="14" t="n"/>
+      <c r="H175" s="12" t="n"/>
+      <c r="I175" s="12" t="n"/>
+      <c r="J175" s="12" t="n"/>
+      <c r="K175" s="12" t="n"/>
+      <c r="L175" s="13" t="n"/>
+      <c r="M175" s="12" t="n"/>
+      <c r="N175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n"/>
@@ -3047,7 +4146,13 @@
         <f>IF(A176="","",COUNTIF(招式表!$A$2:$A$201,A176))</f>
         <v/>
       </c>
-      <c r="H176" s="14" t="n"/>
+      <c r="H176" s="12" t="n"/>
+      <c r="I176" s="12" t="n"/>
+      <c r="J176" s="12" t="n"/>
+      <c r="K176" s="12" t="n"/>
+      <c r="L176" s="13" t="n"/>
+      <c r="M176" s="12" t="n"/>
+      <c r="N176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n"/>
@@ -3060,7 +4165,13 @@
         <f>IF(A177="","",COUNTIF(招式表!$A$2:$A$201,A177))</f>
         <v/>
       </c>
-      <c r="H177" s="14" t="n"/>
+      <c r="H177" s="12" t="n"/>
+      <c r="I177" s="12" t="n"/>
+      <c r="J177" s="12" t="n"/>
+      <c r="K177" s="12" t="n"/>
+      <c r="L177" s="13" t="n"/>
+      <c r="M177" s="12" t="n"/>
+      <c r="N177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="n"/>
@@ -3073,7 +4184,13 @@
         <f>IF(A178="","",COUNTIF(招式表!$A$2:$A$201,A178))</f>
         <v/>
       </c>
-      <c r="H178" s="14" t="n"/>
+      <c r="H178" s="12" t="n"/>
+      <c r="I178" s="12" t="n"/>
+      <c r="J178" s="12" t="n"/>
+      <c r="K178" s="12" t="n"/>
+      <c r="L178" s="13" t="n"/>
+      <c r="M178" s="12" t="n"/>
+      <c r="N178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="n"/>
@@ -3086,7 +4203,13 @@
         <f>IF(A179="","",COUNTIF(招式表!$A$2:$A$201,A179))</f>
         <v/>
       </c>
-      <c r="H179" s="14" t="n"/>
+      <c r="H179" s="12" t="n"/>
+      <c r="I179" s="12" t="n"/>
+      <c r="J179" s="12" t="n"/>
+      <c r="K179" s="12" t="n"/>
+      <c r="L179" s="13" t="n"/>
+      <c r="M179" s="12" t="n"/>
+      <c r="N179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="n"/>
@@ -3099,7 +4222,13 @@
         <f>IF(A180="","",COUNTIF(招式表!$A$2:$A$201,A180))</f>
         <v/>
       </c>
-      <c r="H180" s="14" t="n"/>
+      <c r="H180" s="12" t="n"/>
+      <c r="I180" s="12" t="n"/>
+      <c r="J180" s="12" t="n"/>
+      <c r="K180" s="12" t="n"/>
+      <c r="L180" s="13" t="n"/>
+      <c r="M180" s="12" t="n"/>
+      <c r="N180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="n"/>
@@ -3112,7 +4241,13 @@
         <f>IF(A181="","",COUNTIF(招式表!$A$2:$A$201,A181))</f>
         <v/>
       </c>
-      <c r="H181" s="14" t="n"/>
+      <c r="H181" s="12" t="n"/>
+      <c r="I181" s="12" t="n"/>
+      <c r="J181" s="12" t="n"/>
+      <c r="K181" s="12" t="n"/>
+      <c r="L181" s="13" t="n"/>
+      <c r="M181" s="12" t="n"/>
+      <c r="N181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n"/>
@@ -3125,7 +4260,13 @@
         <f>IF(A182="","",COUNTIF(招式表!$A$2:$A$201,A182))</f>
         <v/>
       </c>
-      <c r="H182" s="14" t="n"/>
+      <c r="H182" s="12" t="n"/>
+      <c r="I182" s="12" t="n"/>
+      <c r="J182" s="12" t="n"/>
+      <c r="K182" s="12" t="n"/>
+      <c r="L182" s="13" t="n"/>
+      <c r="M182" s="12" t="n"/>
+      <c r="N182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n"/>
@@ -3138,7 +4279,13 @@
         <f>IF(A183="","",COUNTIF(招式表!$A$2:$A$201,A183))</f>
         <v/>
       </c>
-      <c r="H183" s="14" t="n"/>
+      <c r="H183" s="12" t="n"/>
+      <c r="I183" s="12" t="n"/>
+      <c r="J183" s="12" t="n"/>
+      <c r="K183" s="12" t="n"/>
+      <c r="L183" s="13" t="n"/>
+      <c r="M183" s="12" t="n"/>
+      <c r="N183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="n"/>
@@ -3151,7 +4298,13 @@
         <f>IF(A184="","",COUNTIF(招式表!$A$2:$A$201,A184))</f>
         <v/>
       </c>
-      <c r="H184" s="14" t="n"/>
+      <c r="H184" s="12" t="n"/>
+      <c r="I184" s="12" t="n"/>
+      <c r="J184" s="12" t="n"/>
+      <c r="K184" s="12" t="n"/>
+      <c r="L184" s="13" t="n"/>
+      <c r="M184" s="12" t="n"/>
+      <c r="N184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="n"/>
@@ -3164,7 +4317,13 @@
         <f>IF(A185="","",COUNTIF(招式表!$A$2:$A$201,A185))</f>
         <v/>
       </c>
-      <c r="H185" s="14" t="n"/>
+      <c r="H185" s="12" t="n"/>
+      <c r="I185" s="12" t="n"/>
+      <c r="J185" s="12" t="n"/>
+      <c r="K185" s="12" t="n"/>
+      <c r="L185" s="13" t="n"/>
+      <c r="M185" s="12" t="n"/>
+      <c r="N185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="n"/>
@@ -3177,7 +4336,13 @@
         <f>IF(A186="","",COUNTIF(招式表!$A$2:$A$201,A186))</f>
         <v/>
       </c>
-      <c r="H186" s="14" t="n"/>
+      <c r="H186" s="12" t="n"/>
+      <c r="I186" s="12" t="n"/>
+      <c r="J186" s="12" t="n"/>
+      <c r="K186" s="12" t="n"/>
+      <c r="L186" s="13" t="n"/>
+      <c r="M186" s="12" t="n"/>
+      <c r="N186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="n"/>
@@ -3190,7 +4355,13 @@
         <f>IF(A187="","",COUNTIF(招式表!$A$2:$A$201,A187))</f>
         <v/>
       </c>
-      <c r="H187" s="14" t="n"/>
+      <c r="H187" s="12" t="n"/>
+      <c r="I187" s="12" t="n"/>
+      <c r="J187" s="12" t="n"/>
+      <c r="K187" s="12" t="n"/>
+      <c r="L187" s="13" t="n"/>
+      <c r="M187" s="12" t="n"/>
+      <c r="N187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="n"/>
@@ -3203,7 +4374,13 @@
         <f>IF(A188="","",COUNTIF(招式表!$A$2:$A$201,A188))</f>
         <v/>
       </c>
-      <c r="H188" s="14" t="n"/>
+      <c r="H188" s="12" t="n"/>
+      <c r="I188" s="12" t="n"/>
+      <c r="J188" s="12" t="n"/>
+      <c r="K188" s="12" t="n"/>
+      <c r="L188" s="13" t="n"/>
+      <c r="M188" s="12" t="n"/>
+      <c r="N188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="n"/>
@@ -3216,7 +4393,13 @@
         <f>IF(A189="","",COUNTIF(招式表!$A$2:$A$201,A189))</f>
         <v/>
       </c>
-      <c r="H189" s="14" t="n"/>
+      <c r="H189" s="12" t="n"/>
+      <c r="I189" s="12" t="n"/>
+      <c r="J189" s="12" t="n"/>
+      <c r="K189" s="12" t="n"/>
+      <c r="L189" s="13" t="n"/>
+      <c r="M189" s="12" t="n"/>
+      <c r="N189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="n"/>
@@ -3229,7 +4412,13 @@
         <f>IF(A190="","",COUNTIF(招式表!$A$2:$A$201,A190))</f>
         <v/>
       </c>
-      <c r="H190" s="14" t="n"/>
+      <c r="H190" s="12" t="n"/>
+      <c r="I190" s="12" t="n"/>
+      <c r="J190" s="12" t="n"/>
+      <c r="K190" s="12" t="n"/>
+      <c r="L190" s="13" t="n"/>
+      <c r="M190" s="12" t="n"/>
+      <c r="N190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="n"/>
@@ -3242,7 +4431,13 @@
         <f>IF(A191="","",COUNTIF(招式表!$A$2:$A$201,A191))</f>
         <v/>
       </c>
-      <c r="H191" s="14" t="n"/>
+      <c r="H191" s="12" t="n"/>
+      <c r="I191" s="12" t="n"/>
+      <c r="J191" s="12" t="n"/>
+      <c r="K191" s="12" t="n"/>
+      <c r="L191" s="13" t="n"/>
+      <c r="M191" s="12" t="n"/>
+      <c r="N191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="n"/>
@@ -3255,7 +4450,13 @@
         <f>IF(A192="","",COUNTIF(招式表!$A$2:$A$201,A192))</f>
         <v/>
       </c>
-      <c r="H192" s="14" t="n"/>
+      <c r="H192" s="12" t="n"/>
+      <c r="I192" s="12" t="n"/>
+      <c r="J192" s="12" t="n"/>
+      <c r="K192" s="12" t="n"/>
+      <c r="L192" s="13" t="n"/>
+      <c r="M192" s="12" t="n"/>
+      <c r="N192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="n"/>
@@ -3268,7 +4469,13 @@
         <f>IF(A193="","",COUNTIF(招式表!$A$2:$A$201,A193))</f>
         <v/>
       </c>
-      <c r="H193" s="14" t="n"/>
+      <c r="H193" s="12" t="n"/>
+      <c r="I193" s="12" t="n"/>
+      <c r="J193" s="12" t="n"/>
+      <c r="K193" s="12" t="n"/>
+      <c r="L193" s="13" t="n"/>
+      <c r="M193" s="12" t="n"/>
+      <c r="N193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="n"/>
@@ -3281,7 +4488,13 @@
         <f>IF(A194="","",COUNTIF(招式表!$A$2:$A$201,A194))</f>
         <v/>
       </c>
-      <c r="H194" s="14" t="n"/>
+      <c r="H194" s="12" t="n"/>
+      <c r="I194" s="12" t="n"/>
+      <c r="J194" s="12" t="n"/>
+      <c r="K194" s="12" t="n"/>
+      <c r="L194" s="13" t="n"/>
+      <c r="M194" s="12" t="n"/>
+      <c r="N194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="n"/>
@@ -3294,7 +4507,13 @@
         <f>IF(A195="","",COUNTIF(招式表!$A$2:$A$201,A195))</f>
         <v/>
       </c>
-      <c r="H195" s="14" t="n"/>
+      <c r="H195" s="12" t="n"/>
+      <c r="I195" s="12" t="n"/>
+      <c r="J195" s="12" t="n"/>
+      <c r="K195" s="12" t="n"/>
+      <c r="L195" s="13" t="n"/>
+      <c r="M195" s="12" t="n"/>
+      <c r="N195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="n"/>
@@ -3307,7 +4526,13 @@
         <f>IF(A196="","",COUNTIF(招式表!$A$2:$A$201,A196))</f>
         <v/>
       </c>
-      <c r="H196" s="14" t="n"/>
+      <c r="H196" s="12" t="n"/>
+      <c r="I196" s="12" t="n"/>
+      <c r="J196" s="12" t="n"/>
+      <c r="K196" s="12" t="n"/>
+      <c r="L196" s="13" t="n"/>
+      <c r="M196" s="12" t="n"/>
+      <c r="N196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="12" t="n"/>
@@ -3320,7 +4545,13 @@
         <f>IF(A197="","",COUNTIF(招式表!$A$2:$A$201,A197))</f>
         <v/>
       </c>
-      <c r="H197" s="14" t="n"/>
+      <c r="H197" s="12" t="n"/>
+      <c r="I197" s="12" t="n"/>
+      <c r="J197" s="12" t="n"/>
+      <c r="K197" s="12" t="n"/>
+      <c r="L197" s="13" t="n"/>
+      <c r="M197" s="12" t="n"/>
+      <c r="N197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="n"/>
@@ -3333,7 +4564,13 @@
         <f>IF(A198="","",COUNTIF(招式表!$A$2:$A$201,A198))</f>
         <v/>
       </c>
-      <c r="H198" s="14" t="n"/>
+      <c r="H198" s="12" t="n"/>
+      <c r="I198" s="12" t="n"/>
+      <c r="J198" s="12" t="n"/>
+      <c r="K198" s="12" t="n"/>
+      <c r="L198" s="13" t="n"/>
+      <c r="M198" s="12" t="n"/>
+      <c r="N198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="n"/>
@@ -3346,7 +4583,13 @@
         <f>IF(A199="","",COUNTIF(招式表!$A$2:$A$201,A199))</f>
         <v/>
       </c>
-      <c r="H199" s="14" t="n"/>
+      <c r="H199" s="12" t="n"/>
+      <c r="I199" s="12" t="n"/>
+      <c r="J199" s="12" t="n"/>
+      <c r="K199" s="12" t="n"/>
+      <c r="L199" s="13" t="n"/>
+      <c r="M199" s="12" t="n"/>
+      <c r="N199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="n"/>
@@ -3359,7 +4602,13 @@
         <f>IF(A200="","",COUNTIF(招式表!$A$2:$A$201,A200))</f>
         <v/>
       </c>
-      <c r="H200" s="14" t="n"/>
+      <c r="H200" s="12" t="n"/>
+      <c r="I200" s="12" t="n"/>
+      <c r="J200" s="12" t="n"/>
+      <c r="K200" s="12" t="n"/>
+      <c r="L200" s="13" t="n"/>
+      <c r="M200" s="12" t="n"/>
+      <c r="N200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="n"/>
@@ -3372,19 +4621,48 @@
         <f>IF(A201="","",COUNTIF(招式表!$A$2:$A$201,A201))</f>
         <v/>
       </c>
-      <c r="H201" s="14" t="n"/>
+      <c r="H201" s="12" t="n"/>
+      <c r="I201" s="12" t="n"/>
+      <c r="J201" s="12" t="n"/>
+      <c r="K201" s="12" t="n"/>
+      <c r="L201" s="13" t="n"/>
+      <c r="M201" s="12" t="n"/>
+      <c r="N201" s="14" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="9">
     <dataValidation sqref="C2:C201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
       <formula1>=選單!$A$1:$A$24</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
       <formula1>=選單!$F$1:$F$2</formula1>
     </dataValidation>
+    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
+      <formula1>=選單!$G$1:$G$2</formula1>
+    </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 200 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="L2:L201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 300 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3562,16 +4840,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" s="15">
         <f>IF(A2="","",IFERROR(INDEX(武功總表!$E$2:$E$201,MATCH(A2,武功總表!$A$2:$A$201,0)),0)+N(H2))</f>
@@ -3634,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>0</v>
@@ -3703,19 +4981,19 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>7</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4" s="15">
         <f>IF(A4="","",IFERROR(INDEX(武功總表!$E$2:$E$201,MATCH(A4,武功總表!$A$2:$A$201,0)),0)+N(H4))</f>
@@ -3736,7 +5014,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>格擋成功後</t>
+          <t>無</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr"/>
@@ -3771,23 +5049,23 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>中門破陣</t>
+          <t>中門直進</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I5" s="15">
         <f>IF(A5="","",IFERROR(INDEX(武功總表!$E$2:$E$201,MATCH(A5,武功總表!$A$2:$A$201,0)),0)+N(H5))</f>
@@ -3804,7 +5082,7 @@
         </is>
       </c>
       <c r="L5" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
@@ -3820,18 +5098,12 @@
       </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
-          <t>破防</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v>10</v>
-      </c>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="8" t="n"/>
+      <c r="T5" s="8" t="n"/>
       <c r="U5" s="11" t="inlineStr">
         <is>
           <t>範例</t>
@@ -3853,16 +5125,16 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>0</v>
@@ -3882,11 +5154,11 @@
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>閃躲成功後</t>
+          <t>無</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
@@ -3911,86 +5183,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>sanmeendo</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>三門齊開</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="n"/>
       <c r="I7" s="15">
         <f>IF(A7="","",IFERROR(INDEX(武功總表!$E$2:$E$201,MATCH(A7,武功總表!$A$2:$A$201,0)),0)+N(H7))</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>割傷</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>連招</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>開門見山,側門截勢,反門回刃</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>流血</t>
-        </is>
-      </c>
-      <c r="R7" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" s="11" t="inlineStr">
-        <is>
-          <t>範例：特效數字為建議值</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="13" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -9113,7 +10329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9318,108 +10534,133 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>【招式表】</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr"/>
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>武術造詣係數</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>武功每升一級，給「武術造詣」= 新等級 × 係數。（龍圖心經用的是 10）</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>0～100</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>0（不給）</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>有（龍圖心經）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>武功代號</t>
+          <t>武學之道起始等級</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>這一招屬於哪套武功，從「武功總表」已建立的代號中選。</t>
+          <t>武功練到這個等級後，每升一級開始給「武學之道」。</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>0～200</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>（必填）</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr"/>
+          <t>不給</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>有（龍圖心經 50 級）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>順序</t>
+          <t>武學之道係數</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>招式的編號，用來對應第一部分寫的招式敘述。</t>
+          <t>給「武學之道」=（新等級 − 起始等級 + 1）× 係數。</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>1～30</t>
+          <t>0～100</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>（必填）</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>有（龍圖心經）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>招式名</t>
+          <t>整套特效</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>例如「三門齊開」。不用加「」。</t>
+          <t>整套武功共有的特殊效果。
+「三招重演」：連續三招都命中後，有機會把這三招快速再使一次（三門刀法）。</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>（必填）</t>
+          <t>無</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>解鎖等級</t>
+          <t>整套特效機率</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>武功練到幾級才會使出這一招。</t>
+          <t>條件達成時發動的機率。</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>0～200</t>
+          <t>0～100</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>0（一開始就會）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -9431,176 +10672,160 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>命中加成</t>
+          <t>整套特效強度</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>加在命中判定上。越高越容易打中。程式欄位 attack。</t>
+          <t>三招重演：重演那三招的傷害 %，100 = 和平常一樣。</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>-30～30</t>
+          <t>0～300</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>防守加成</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>出這招後，對手下一招比較難打中你。程式欄位 defense。</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>-30～30</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>【招式表】</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr"/>
+      <c r="C15" s="18" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
+      <c r="E15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>內力加成</t>
+          <t>武功代號</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>有運內功時，額外增加的內力力道。程式欄位 force。</t>
+          <t>這一招屬於哪套武功，從「武功總表」已建立的代號中選。</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>-30～30</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
+          <t>（必填）</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>招式傷害加成</t>
+          <t>順序</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>這一招自己的傷害加成，會和整套加成相加。可以填負數，代表這招傷害比較低（例如防守招）。</t>
+          <t>招式的編號，用來對應第一部分寫的招式敘述。</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>-50～100</t>
+          <t>1～30</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+          <t>（必填）</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>總傷害加成</t>
+          <t>招式名</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>自動計算 = 整套加成 + 招式加成。</t>
+          <t>例如「三門齊開」。不用加「」。</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>（自動）</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr"/>
-      <c r="E18" s="19" t="inlineStr"/>
+          <t>中文</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>（必填）</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>傷害類型</t>
+          <t>解鎖等級</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>影響戰鬥訊息的用字，例如「割傷」會顯示「造成一道輕微的傷口」之類。</t>
+          <t>武功練到幾級才會使出這一招。</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>0～200</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>割傷（刀）</t>
+          <t>0（一開始就會）</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>元素</t>
+          <t>命中加成</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>招式帶火、冰、雷、風屬性時，打中後會再加上裝備的同元素傷害。</t>
+          <t>加在命中判定上。越高越容易打中。程式欄位 attack。</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>-30～30</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>無</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -9612,139 +10837,139 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>出招權重</t>
+          <t>防守加成</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>這招被選中的機率。5 是普通，10 是很常出，1 是很少出。</t>
+          <t>出這招後，對手下一招比較難打中你。程式欄位 defense。</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>1～10</t>
+          <t>-30～30</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>出招條件</t>
+          <t>內力加成</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>只在特定情況才會出的招，例如對手重傷時的殺招、格擋成功後的反擊。</t>
+          <t>有運內功時，額外增加的內力力道。程式欄位 force。</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>-30～30</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>無（隨時都可能出）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>連招前置</t>
+          <t>招式傷害加成</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>出招條件選「連招」時才需要填：最近幾回合內要先用過哪些招，用逗號分隔。</t>
+          <t>這一招自己的傷害加成，會和整套加成相加。可以填負數，代表這招傷害比較低（例如防守招）。</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>招式名</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr"/>
-      <c r="E23" s="19" t="inlineStr"/>
+          <t>-50～100</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>內力消耗</t>
+          <t>總傷害加成</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>使出這招要扣多少內力。內力不夠就不會出這招。</t>
+          <t>自動計算 = 整套加成 + 招式加成。</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>0～500</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+          <t>（自動）</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>冷卻</t>
+          <t>傷害類型</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>使出後要隔幾回合才能再出。</t>
+          <t>影響戰鬥訊息的用字，例如「割傷」會顯示「造成一道輕微的傷口」之類。</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>0～20</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>0（沒有冷卻）</t>
+          <t>割傷（刀）</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>打中後的附加效果，見下方特效說明。</t>
+          <t>招式帶火、冰、雷、風屬性時，打中後會再加上裝備的同元素傷害。</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
@@ -9759,29 +10984,29 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>特效機率</t>
+          <t>出招權重</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>打中時發動特效的機率。</t>
+          <t>這招被選中的機率。5 是普通，10 是很常出，1 是很少出。</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
+          <t>1～10</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -9793,22 +11018,22 @@
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>特效持續</t>
+          <t>出招條件</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>特效持續幾回合（追擊、震退這類一次性的不用填）。</t>
+          <t>只在特定情況才會出的招，例如對手重傷時的殺招、格擋成功後的反擊。</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>0～20</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>無（隨時都可能出）</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -9820,164 +11045,318 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>特效強度</t>
+          <t>連招前置</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>依特效不同意思不同，見下方。</t>
+          <t>出招條件選「連招」時才需要填：最近幾回合內要先用過哪些招，用逗號分隔。</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>依特效</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+          <t>招式名</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr"/>
+      <c r="E29" s="19" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>備註</t>
+          <t>內力消耗</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>任何想說明的事。</t>
+          <t>使出這招要扣多少內力。內力不夠就不會出這招。</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr"/>
-      <c r="E30" s="19" t="inlineStr"/>
+          <t>0～500</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>【特效說明】</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="18" t="inlineStr"/>
-      <c r="D31" s="18" t="inlineStr"/>
-      <c r="E31" s="18" t="inlineStr"/>
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>冷卻</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>使出後要隔幾回合才能再出。</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>0～20</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>0（沒有冷卻）</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>流血</t>
+          <t>特效</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>每回合扣血。強度 = 每回合扣多少點。</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr"/>
-      <c r="D32" s="19" t="inlineStr"/>
-      <c r="E32" s="19" t="inlineStr"/>
+          <t>打中後的附加效果，見下方特效說明。</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>下拉選單</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>破防</t>
+          <t>特效機率</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>對手防具效果降低。強度 = 降低幾 %。</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr"/>
-      <c r="D33" s="19" t="inlineStr"/>
-      <c r="E33" s="19" t="inlineStr"/>
+          <t>打中時發動特效的機率。</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>0～100</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>暈眩</t>
+          <t>特效持續</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>對手停手不能出招。強度不用填。</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr"/>
-      <c r="D34" s="19" t="inlineStr"/>
-      <c r="E34" s="19" t="inlineStr"/>
+          <t>特效持續幾回合（追擊、震退這類一次性的不用填）。</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>0～20</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>緩速</t>
+          <t>特效強度</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>對手出招變慢、閃躲降低。強度 = 降低幾 %。</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr"/>
-      <c r="D35" s="19" t="inlineStr"/>
-      <c r="E35" s="19" t="inlineStr"/>
+          <t>依特效不同意思不同，見下方。</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>0～100</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>依特效</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>吸血</t>
+          <t>備註</t>
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>打中時回復自己的氣。強度 = 回復傷害的幾 %。</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr"/>
+          <t>任何想說明的事。</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
       <c r="D36" s="19" t="inlineStr"/>
       <c r="E36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>追擊</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>立刻再出一招（像瘋虎刀法的追擊）。強度 = 追擊招的傷害 %，100 = 一般傷害。</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr"/>
-      <c r="D37" s="19" t="inlineStr"/>
-      <c r="E37" s="19" t="inlineStr"/>
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>【特效說明】</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr"/>
+      <c r="C37" s="18" t="inlineStr"/>
+      <c r="D37" s="18" t="inlineStr"/>
+      <c r="E37" s="18" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>震退</t>
+          <t>流血</t>
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>讓對手忙亂一回合。強度不用填。</t>
+          <t>每回合扣血。強度 = 每回合扣多少點。</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr"/>
       <c r="D38" s="19" t="inlineStr"/>
       <c r="E38" s="19" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>破防</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>對手防具效果降低。強度 = 降低幾 %。</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr"/>
+      <c r="D39" s="19" t="inlineStr"/>
+      <c r="E39" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>暈眩</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>對手停手不能出招。強度不用填。</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr"/>
+      <c r="D40" s="19" t="inlineStr"/>
+      <c r="E40" s="19" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>緩速</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>對手出招變慢、閃躲降低。強度 = 降低幾 %。</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr"/>
+      <c r="D41" s="19" t="inlineStr"/>
+      <c r="E41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>吸血</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>打中時回復自己的氣。強度 = 回復傷害的幾 %。</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr"/>
+      <c r="D42" s="19" t="inlineStr"/>
+      <c r="E42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>追擊</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>立刻再出一招（像瘋虎刀法的追擊）。強度 = 追擊招的傷害 %，100 = 一般傷害。</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr"/>
+      <c r="D43" s="19" t="inlineStr"/>
+      <c r="E43" s="19" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>震退</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>讓對手忙亂一回合。強度不用填。</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="19" t="inlineStr"/>
+      <c r="E44" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10276,7 +11655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10310,6 +11689,11 @@
           <t>固定</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10340,6 +11724,11 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>隨等級成長</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>三招重演</t>
         </is>
       </c>
     </row>

--- a/docs/martial_arts/武功強度設定表.xlsx
+++ b/docs/martial_arts/武功強度設定表.xlsx
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="L2" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>範例：數字皆為建議值</t>
+          <t>三招重演：機率 = 10% + 天生膽識÷4；需三門刀法 100、狻猊步法 60（enable）</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       <c r="B12" s="20" t="inlineStr">
         <is>
           <t>整套武功共有的特殊效果。
-「三招重演」：連續三招都命中後，有機會把這三招快速再使一次（三門刀法）。</t>
+「三招重演」（三門刀法）：最近三招都命中時，有機會立即把這三招再使一次；重演必中（不會被閃開或格開，防具照樣減傷），重演的招不算連中，發動後連中紀錄歸零。</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>條件達成時發動的機率。</t>
+          <t>條件達成時發動的基本機率。三招重演另加「天生膽識÷4」（小數捨去，不含裝備），寫在備註。</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>三招重演：重演那三招的傷害 %，100 = 和平常一樣。</t>
+          <t>三招重演：重演那三招的傷害 %，以那招平常的傷害（含各種加成）為準，100 = 和平常一樣。</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">

--- a/docs/martial_arts/武功強度設定表.xlsx
+++ b/docs/martial_arts/武功強度設定表.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N201"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -702,10 +702,11 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -763,27 +764,33 @@
       <c r="J1" s="7" t="inlineStr">
         <is>
           <t>武學之道
+減數</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>武學之道
 係數</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>整套特效</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>整套特效
 機率 (%)</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>整套特效
 強度</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -823,26 +830,29 @@
         <v/>
       </c>
       <c r="H2" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>30</v>
       </c>
       <c r="J2" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>三招重演</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>三招重演</t>
-        </is>
-      </c>
-      <c r="L2" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" s="8" t="n">
+      <c r="N2" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="O2" s="11" t="inlineStr">
         <is>
           <t>三招重演：機率 = 10% + 天生膽識÷4；需三門刀法 100、狻猊步法 60（enable）</t>
         </is>
@@ -863,9 +873,10 @@
       <c r="I3" s="12" t="n"/>
       <c r="J3" s="12" t="n"/>
       <c r="K3" s="12" t="n"/>
-      <c r="L3" s="13" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="14" t="n"/>
+      <c r="L3" s="12" t="n"/>
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -882,9 +893,10 @@
       <c r="I4" s="12" t="n"/>
       <c r="J4" s="12" t="n"/>
       <c r="K4" s="12" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="14" t="n"/>
+      <c r="L4" s="12" t="n"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="12" t="n"/>
+      <c r="O4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n"/>
@@ -901,9 +913,10 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="14" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -920,9 +933,10 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="14" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n"/>
@@ -939,9 +953,10 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="14" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -958,9 +973,10 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="14" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n"/>
@@ -977,9 +993,10 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="14" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -996,9 +1013,10 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="14" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n"/>
@@ -1015,9 +1033,10 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="14" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -1034,9 +1053,10 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="14" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n"/>
@@ -1053,9 +1073,10 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="14" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -1072,9 +1093,10 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="14" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n"/>
@@ -1091,9 +1113,10 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="14" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1110,9 +1133,10 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="14" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n"/>
@@ -1129,9 +1153,10 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="14" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -1148,9 +1173,10 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="14" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n"/>
@@ -1167,9 +1193,10 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="14" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1186,9 +1213,10 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="14" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
@@ -1205,9 +1233,10 @@
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="14" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1224,9 +1253,10 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
-      <c r="L22" s="13" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="14" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n"/>
@@ -1243,9 +1273,10 @@
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="14" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1262,9 +1293,10 @@
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="14" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n"/>
@@ -1281,9 +1313,10 @@
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
       <c r="K25" s="12" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="14" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1300,9 +1333,10 @@
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="14" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n"/>
@@ -1319,9 +1353,10 @@
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="14" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1338,9 +1373,10 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="14" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n"/>
@@ -1357,9 +1393,10 @@
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="12" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="14" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1376,9 +1413,10 @@
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
       <c r="K30" s="12" t="n"/>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="14" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n"/>
@@ -1395,9 +1433,10 @@
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
       <c r="K31" s="12" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="14" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1414,9 +1453,10 @@
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
       <c r="K32" s="12" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="14" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n"/>
@@ -1433,9 +1473,10 @@
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
       <c r="K33" s="12" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="14" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1452,9 +1493,10 @@
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
       <c r="K34" s="12" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="14" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n"/>
@@ -1471,9 +1513,10 @@
       <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
       <c r="K35" s="12" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="14" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="13" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1490,9 +1533,10 @@
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="12" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="14" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n"/>
@@ -1509,9 +1553,10 @@
       <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
       <c r="K37" s="12" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="14" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="13" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1528,9 +1573,10 @@
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
       <c r="K38" s="12" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="14" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n"/>
@@ -1547,9 +1593,10 @@
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
       <c r="K39" s="12" t="n"/>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="14" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="13" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -1566,9 +1613,10 @@
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
       <c r="K40" s="12" t="n"/>
-      <c r="L40" s="13" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="14" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="13" t="n"/>
+      <c r="N40" s="12" t="n"/>
+      <c r="O40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n"/>
@@ -1585,9 +1633,10 @@
       <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
       <c r="K41" s="12" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="14" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="13" t="n"/>
+      <c r="N41" s="12" t="n"/>
+      <c r="O41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -1604,9 +1653,10 @@
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
       <c r="K42" s="12" t="n"/>
-      <c r="L42" s="13" t="n"/>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="14" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="13" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n"/>
@@ -1623,9 +1673,10 @@
       <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
       <c r="K43" s="12" t="n"/>
-      <c r="L43" s="13" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="14" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="13" t="n"/>
+      <c r="N43" s="12" t="n"/>
+      <c r="O43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -1642,9 +1693,10 @@
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
       <c r="K44" s="12" t="n"/>
-      <c r="L44" s="13" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="14" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n"/>
@@ -1661,9 +1713,10 @@
       <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
       <c r="K45" s="12" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="14" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="13" t="n"/>
+      <c r="N45" s="12" t="n"/>
+      <c r="O45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -1680,9 +1733,10 @@
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
       <c r="K46" s="12" t="n"/>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="14" t="n"/>
+      <c r="L46" s="12" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="12" t="n"/>
+      <c r="O46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="n"/>
@@ -1699,9 +1753,10 @@
       <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
       <c r="K47" s="12" t="n"/>
-      <c r="L47" s="13" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="14" t="n"/>
+      <c r="L47" s="12" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="12" t="n"/>
+      <c r="O47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -1718,9 +1773,10 @@
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
       <c r="K48" s="12" t="n"/>
-      <c r="L48" s="13" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="14" t="n"/>
+      <c r="L48" s="12" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="12" t="n"/>
+      <c r="O48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n"/>
@@ -1737,9 +1793,10 @@
       <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
       <c r="K49" s="12" t="n"/>
-      <c r="L49" s="13" t="n"/>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="14" t="n"/>
+      <c r="L49" s="12" t="n"/>
+      <c r="M49" s="13" t="n"/>
+      <c r="N49" s="12" t="n"/>
+      <c r="O49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -1756,9 +1813,10 @@
       <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
       <c r="K50" s="12" t="n"/>
-      <c r="L50" s="13" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="14" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n"/>
@@ -1775,9 +1833,10 @@
       <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
       <c r="K51" s="12" t="n"/>
-      <c r="L51" s="13" t="n"/>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="14" t="n"/>
+      <c r="L51" s="12" t="n"/>
+      <c r="M51" s="13" t="n"/>
+      <c r="N51" s="12" t="n"/>
+      <c r="O51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -1794,9 +1853,10 @@
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
       <c r="K52" s="12" t="n"/>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="14" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n"/>
@@ -1813,9 +1873,10 @@
       <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
       <c r="K53" s="12" t="n"/>
-      <c r="L53" s="13" t="n"/>
-      <c r="M53" s="12" t="n"/>
-      <c r="N53" s="14" t="n"/>
+      <c r="L53" s="12" t="n"/>
+      <c r="M53" s="13" t="n"/>
+      <c r="N53" s="12" t="n"/>
+      <c r="O53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -1832,9 +1893,10 @@
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
       <c r="K54" s="12" t="n"/>
-      <c r="L54" s="13" t="n"/>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="14" t="n"/>
+      <c r="L54" s="12" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="12" t="n"/>
+      <c r="O54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n"/>
@@ -1851,9 +1913,10 @@
       <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
       <c r="K55" s="12" t="n"/>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="14" t="n"/>
+      <c r="L55" s="12" t="n"/>
+      <c r="M55" s="13" t="n"/>
+      <c r="N55" s="12" t="n"/>
+      <c r="O55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -1870,9 +1933,10 @@
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
       <c r="K56" s="12" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="12" t="n"/>
-      <c r="N56" s="14" t="n"/>
+      <c r="L56" s="12" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="12" t="n"/>
+      <c r="O56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n"/>
@@ -1889,9 +1953,10 @@
       <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
       <c r="K57" s="12" t="n"/>
-      <c r="L57" s="13" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="14" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="13" t="n"/>
+      <c r="N57" s="12" t="n"/>
+      <c r="O57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -1908,9 +1973,10 @@
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
       <c r="K58" s="12" t="n"/>
-      <c r="L58" s="13" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="14" t="n"/>
+      <c r="L58" s="12" t="n"/>
+      <c r="M58" s="13" t="n"/>
+      <c r="N58" s="12" t="n"/>
+      <c r="O58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n"/>
@@ -1927,9 +1993,10 @@
       <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
       <c r="K59" s="12" t="n"/>
-      <c r="L59" s="13" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="14" t="n"/>
+      <c r="L59" s="12" t="n"/>
+      <c r="M59" s="13" t="n"/>
+      <c r="N59" s="12" t="n"/>
+      <c r="O59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -1946,9 +2013,10 @@
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
       <c r="K60" s="12" t="n"/>
-      <c r="L60" s="13" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="14" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n"/>
@@ -1965,9 +2033,10 @@
       <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
       <c r="K61" s="12" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="14" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="13" t="n"/>
+      <c r="N61" s="12" t="n"/>
+      <c r="O61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -1984,9 +2053,10 @@
       <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
       <c r="K62" s="12" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="14" t="n"/>
+      <c r="L62" s="12" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="12" t="n"/>
+      <c r="O62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n"/>
@@ -2003,9 +2073,10 @@
       <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
       <c r="K63" s="12" t="n"/>
-      <c r="L63" s="13" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="14" t="n"/>
+      <c r="L63" s="12" t="n"/>
+      <c r="M63" s="13" t="n"/>
+      <c r="N63" s="12" t="n"/>
+      <c r="O63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -2022,9 +2093,10 @@
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
       <c r="K64" s="12" t="n"/>
-      <c r="L64" s="13" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="14" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="13" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="n"/>
@@ -2041,9 +2113,10 @@
       <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
       <c r="K65" s="12" t="n"/>
-      <c r="L65" s="13" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="14" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="13" t="n"/>
+      <c r="N65" s="12" t="n"/>
+      <c r="O65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -2060,9 +2133,10 @@
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
       <c r="K66" s="12" t="n"/>
-      <c r="L66" s="13" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="14" t="n"/>
+      <c r="L66" s="12" t="n"/>
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="12" t="n"/>
+      <c r="O66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="n"/>
@@ -2079,9 +2153,10 @@
       <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
       <c r="K67" s="12" t="n"/>
-      <c r="L67" s="13" t="n"/>
-      <c r="M67" s="12" t="n"/>
-      <c r="N67" s="14" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="13" t="n"/>
+      <c r="N67" s="12" t="n"/>
+      <c r="O67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -2098,9 +2173,10 @@
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
       <c r="K68" s="12" t="n"/>
-      <c r="L68" s="13" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="14" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="13" t="n"/>
+      <c r="N68" s="12" t="n"/>
+      <c r="O68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="n"/>
@@ -2117,9 +2193,10 @@
       <c r="I69" s="12" t="n"/>
       <c r="J69" s="12" t="n"/>
       <c r="K69" s="12" t="n"/>
-      <c r="L69" s="13" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="14" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="13" t="n"/>
+      <c r="N69" s="12" t="n"/>
+      <c r="O69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -2136,9 +2213,10 @@
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
       <c r="K70" s="12" t="n"/>
-      <c r="L70" s="13" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="14" t="n"/>
+      <c r="L70" s="12" t="n"/>
+      <c r="M70" s="13" t="n"/>
+      <c r="N70" s="12" t="n"/>
+      <c r="O70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="n"/>
@@ -2155,9 +2233,10 @@
       <c r="I71" s="12" t="n"/>
       <c r="J71" s="12" t="n"/>
       <c r="K71" s="12" t="n"/>
-      <c r="L71" s="13" t="n"/>
-      <c r="M71" s="12" t="n"/>
-      <c r="N71" s="14" t="n"/>
+      <c r="L71" s="12" t="n"/>
+      <c r="M71" s="13" t="n"/>
+      <c r="N71" s="12" t="n"/>
+      <c r="O71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -2174,9 +2253,10 @@
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
       <c r="K72" s="12" t="n"/>
-      <c r="L72" s="13" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="14" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="12" t="n"/>
+      <c r="O72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n"/>
@@ -2193,9 +2273,10 @@
       <c r="I73" s="12" t="n"/>
       <c r="J73" s="12" t="n"/>
       <c r="K73" s="12" t="n"/>
-      <c r="L73" s="13" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="14" t="n"/>
+      <c r="L73" s="12" t="n"/>
+      <c r="M73" s="13" t="n"/>
+      <c r="N73" s="12" t="n"/>
+      <c r="O73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -2212,9 +2293,10 @@
       <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
       <c r="K74" s="12" t="n"/>
-      <c r="L74" s="13" t="n"/>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="14" t="n"/>
+      <c r="L74" s="12" t="n"/>
+      <c r="M74" s="13" t="n"/>
+      <c r="N74" s="12" t="n"/>
+      <c r="O74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n"/>
@@ -2231,9 +2313,10 @@
       <c r="I75" s="12" t="n"/>
       <c r="J75" s="12" t="n"/>
       <c r="K75" s="12" t="n"/>
-      <c r="L75" s="13" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="14" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="13" t="n"/>
+      <c r="N75" s="12" t="n"/>
+      <c r="O75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -2250,9 +2333,10 @@
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
       <c r="K76" s="12" t="n"/>
-      <c r="L76" s="13" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="14" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="13" t="n"/>
+      <c r="N76" s="12" t="n"/>
+      <c r="O76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n"/>
@@ -2269,9 +2353,10 @@
       <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
       <c r="K77" s="12" t="n"/>
-      <c r="L77" s="13" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="14" t="n"/>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="13" t="n"/>
+      <c r="N77" s="12" t="n"/>
+      <c r="O77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -2288,9 +2373,10 @@
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
       <c r="K78" s="12" t="n"/>
-      <c r="L78" s="13" t="n"/>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="14" t="n"/>
+      <c r="L78" s="12" t="n"/>
+      <c r="M78" s="13" t="n"/>
+      <c r="N78" s="12" t="n"/>
+      <c r="O78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n"/>
@@ -2307,9 +2393,10 @@
       <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
       <c r="K79" s="12" t="n"/>
-      <c r="L79" s="13" t="n"/>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="14" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="13" t="n"/>
+      <c r="N79" s="12" t="n"/>
+      <c r="O79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2326,9 +2413,10 @@
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
       <c r="K80" s="12" t="n"/>
-      <c r="L80" s="13" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="14" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n"/>
@@ -2345,9 +2433,10 @@
       <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
       <c r="K81" s="12" t="n"/>
-      <c r="L81" s="13" t="n"/>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="14" t="n"/>
+      <c r="L81" s="12" t="n"/>
+      <c r="M81" s="13" t="n"/>
+      <c r="N81" s="12" t="n"/>
+      <c r="O81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -2364,9 +2453,10 @@
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
       <c r="K82" s="12" t="n"/>
-      <c r="L82" s="13" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="14" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="13" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n"/>
@@ -2383,9 +2473,10 @@
       <c r="I83" s="12" t="n"/>
       <c r="J83" s="12" t="n"/>
       <c r="K83" s="12" t="n"/>
-      <c r="L83" s="13" t="n"/>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="14" t="n"/>
+      <c r="L83" s="12" t="n"/>
+      <c r="M83" s="13" t="n"/>
+      <c r="N83" s="12" t="n"/>
+      <c r="O83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -2402,9 +2493,10 @@
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
       <c r="K84" s="12" t="n"/>
-      <c r="L84" s="13" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="14" t="n"/>
+      <c r="L84" s="12" t="n"/>
+      <c r="M84" s="13" t="n"/>
+      <c r="N84" s="12" t="n"/>
+      <c r="O84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n"/>
@@ -2421,9 +2513,10 @@
       <c r="I85" s="12" t="n"/>
       <c r="J85" s="12" t="n"/>
       <c r="K85" s="12" t="n"/>
-      <c r="L85" s="13" t="n"/>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="14" t="n"/>
+      <c r="L85" s="12" t="n"/>
+      <c r="M85" s="13" t="n"/>
+      <c r="N85" s="12" t="n"/>
+      <c r="O85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -2440,9 +2533,10 @@
       <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
       <c r="K86" s="12" t="n"/>
-      <c r="L86" s="13" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="14" t="n"/>
+      <c r="L86" s="12" t="n"/>
+      <c r="M86" s="13" t="n"/>
+      <c r="N86" s="12" t="n"/>
+      <c r="O86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n"/>
@@ -2459,9 +2553,10 @@
       <c r="I87" s="12" t="n"/>
       <c r="J87" s="12" t="n"/>
       <c r="K87" s="12" t="n"/>
-      <c r="L87" s="13" t="n"/>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="14" t="n"/>
+      <c r="L87" s="12" t="n"/>
+      <c r="M87" s="13" t="n"/>
+      <c r="N87" s="12" t="n"/>
+      <c r="O87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -2478,9 +2573,10 @@
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
       <c r="K88" s="12" t="n"/>
-      <c r="L88" s="13" t="n"/>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="14" t="n"/>
+      <c r="L88" s="12" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="12" t="n"/>
+      <c r="O88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="n"/>
@@ -2497,9 +2593,10 @@
       <c r="I89" s="12" t="n"/>
       <c r="J89" s="12" t="n"/>
       <c r="K89" s="12" t="n"/>
-      <c r="L89" s="13" t="n"/>
-      <c r="M89" s="12" t="n"/>
-      <c r="N89" s="14" t="n"/>
+      <c r="L89" s="12" t="n"/>
+      <c r="M89" s="13" t="n"/>
+      <c r="N89" s="12" t="n"/>
+      <c r="O89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -2516,9 +2613,10 @@
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="12" t="n"/>
       <c r="K90" s="12" t="n"/>
-      <c r="L90" s="13" t="n"/>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="14" t="n"/>
+      <c r="L90" s="12" t="n"/>
+      <c r="M90" s="13" t="n"/>
+      <c r="N90" s="12" t="n"/>
+      <c r="O90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n"/>
@@ -2535,9 +2633,10 @@
       <c r="I91" s="12" t="n"/>
       <c r="J91" s="12" t="n"/>
       <c r="K91" s="12" t="n"/>
-      <c r="L91" s="13" t="n"/>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="14" t="n"/>
+      <c r="L91" s="12" t="n"/>
+      <c r="M91" s="13" t="n"/>
+      <c r="N91" s="12" t="n"/>
+      <c r="O91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -2554,9 +2653,10 @@
       <c r="I92" s="12" t="n"/>
       <c r="J92" s="12" t="n"/>
       <c r="K92" s="12" t="n"/>
-      <c r="L92" s="13" t="n"/>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="14" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="13" t="n"/>
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n"/>
@@ -2573,9 +2673,10 @@
       <c r="I93" s="12" t="n"/>
       <c r="J93" s="12" t="n"/>
       <c r="K93" s="12" t="n"/>
-      <c r="L93" s="13" t="n"/>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="14" t="n"/>
+      <c r="L93" s="12" t="n"/>
+      <c r="M93" s="13" t="n"/>
+      <c r="N93" s="12" t="n"/>
+      <c r="O93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -2592,9 +2693,10 @@
       <c r="I94" s="12" t="n"/>
       <c r="J94" s="12" t="n"/>
       <c r="K94" s="12" t="n"/>
-      <c r="L94" s="13" t="n"/>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="14" t="n"/>
+      <c r="L94" s="12" t="n"/>
+      <c r="M94" s="13" t="n"/>
+      <c r="N94" s="12" t="n"/>
+      <c r="O94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n"/>
@@ -2611,9 +2713,10 @@
       <c r="I95" s="12" t="n"/>
       <c r="J95" s="12" t="n"/>
       <c r="K95" s="12" t="n"/>
-      <c r="L95" s="13" t="n"/>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="14" t="n"/>
+      <c r="L95" s="12" t="n"/>
+      <c r="M95" s="13" t="n"/>
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -2630,9 +2733,10 @@
       <c r="I96" s="12" t="n"/>
       <c r="J96" s="12" t="n"/>
       <c r="K96" s="12" t="n"/>
-      <c r="L96" s="13" t="n"/>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="14" t="n"/>
+      <c r="L96" s="12" t="n"/>
+      <c r="M96" s="13" t="n"/>
+      <c r="N96" s="12" t="n"/>
+      <c r="O96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n"/>
@@ -2649,9 +2753,10 @@
       <c r="I97" s="12" t="n"/>
       <c r="J97" s="12" t="n"/>
       <c r="K97" s="12" t="n"/>
-      <c r="L97" s="13" t="n"/>
-      <c r="M97" s="12" t="n"/>
-      <c r="N97" s="14" t="n"/>
+      <c r="L97" s="12" t="n"/>
+      <c r="M97" s="13" t="n"/>
+      <c r="N97" s="12" t="n"/>
+      <c r="O97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -2668,9 +2773,10 @@
       <c r="I98" s="12" t="n"/>
       <c r="J98" s="12" t="n"/>
       <c r="K98" s="12" t="n"/>
-      <c r="L98" s="13" t="n"/>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="14" t="n"/>
+      <c r="L98" s="12" t="n"/>
+      <c r="M98" s="13" t="n"/>
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n"/>
@@ -2687,9 +2793,10 @@
       <c r="I99" s="12" t="n"/>
       <c r="J99" s="12" t="n"/>
       <c r="K99" s="12" t="n"/>
-      <c r="L99" s="13" t="n"/>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="14" t="n"/>
+      <c r="L99" s="12" t="n"/>
+      <c r="M99" s="13" t="n"/>
+      <c r="N99" s="12" t="n"/>
+      <c r="O99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -2706,9 +2813,10 @@
       <c r="I100" s="12" t="n"/>
       <c r="J100" s="12" t="n"/>
       <c r="K100" s="12" t="n"/>
-      <c r="L100" s="13" t="n"/>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="14" t="n"/>
+      <c r="L100" s="12" t="n"/>
+      <c r="M100" s="13" t="n"/>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n"/>
@@ -2725,9 +2833,10 @@
       <c r="I101" s="12" t="n"/>
       <c r="J101" s="12" t="n"/>
       <c r="K101" s="12" t="n"/>
-      <c r="L101" s="13" t="n"/>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="14" t="n"/>
+      <c r="L101" s="12" t="n"/>
+      <c r="M101" s="13" t="n"/>
+      <c r="N101" s="12" t="n"/>
+      <c r="O101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -2744,9 +2853,10 @@
       <c r="I102" s="12" t="n"/>
       <c r="J102" s="12" t="n"/>
       <c r="K102" s="12" t="n"/>
-      <c r="L102" s="13" t="n"/>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="14" t="n"/>
+      <c r="L102" s="12" t="n"/>
+      <c r="M102" s="13" t="n"/>
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n"/>
@@ -2763,9 +2873,10 @@
       <c r="I103" s="12" t="n"/>
       <c r="J103" s="12" t="n"/>
       <c r="K103" s="12" t="n"/>
-      <c r="L103" s="13" t="n"/>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="14" t="n"/>
+      <c r="L103" s="12" t="n"/>
+      <c r="M103" s="13" t="n"/>
+      <c r="N103" s="12" t="n"/>
+      <c r="O103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="n"/>
@@ -2782,9 +2893,10 @@
       <c r="I104" s="12" t="n"/>
       <c r="J104" s="12" t="n"/>
       <c r="K104" s="12" t="n"/>
-      <c r="L104" s="13" t="n"/>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="14" t="n"/>
+      <c r="L104" s="12" t="n"/>
+      <c r="M104" s="13" t="n"/>
+      <c r="N104" s="12" t="n"/>
+      <c r="O104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n"/>
@@ -2801,9 +2913,10 @@
       <c r="I105" s="12" t="n"/>
       <c r="J105" s="12" t="n"/>
       <c r="K105" s="12" t="n"/>
-      <c r="L105" s="13" t="n"/>
-      <c r="M105" s="12" t="n"/>
-      <c r="N105" s="14" t="n"/>
+      <c r="L105" s="12" t="n"/>
+      <c r="M105" s="13" t="n"/>
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n"/>
@@ -2820,9 +2933,10 @@
       <c r="I106" s="12" t="n"/>
       <c r="J106" s="12" t="n"/>
       <c r="K106" s="12" t="n"/>
-      <c r="L106" s="13" t="n"/>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="14" t="n"/>
+      <c r="L106" s="12" t="n"/>
+      <c r="M106" s="13" t="n"/>
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n"/>
@@ -2839,9 +2953,10 @@
       <c r="I107" s="12" t="n"/>
       <c r="J107" s="12" t="n"/>
       <c r="K107" s="12" t="n"/>
-      <c r="L107" s="13" t="n"/>
-      <c r="M107" s="12" t="n"/>
-      <c r="N107" s="14" t="n"/>
+      <c r="L107" s="12" t="n"/>
+      <c r="M107" s="13" t="n"/>
+      <c r="N107" s="12" t="n"/>
+      <c r="O107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="n"/>
@@ -2858,9 +2973,10 @@
       <c r="I108" s="12" t="n"/>
       <c r="J108" s="12" t="n"/>
       <c r="K108" s="12" t="n"/>
-      <c r="L108" s="13" t="n"/>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="14" t="n"/>
+      <c r="L108" s="12" t="n"/>
+      <c r="M108" s="13" t="n"/>
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="n"/>
@@ -2877,9 +2993,10 @@
       <c r="I109" s="12" t="n"/>
       <c r="J109" s="12" t="n"/>
       <c r="K109" s="12" t="n"/>
-      <c r="L109" s="13" t="n"/>
-      <c r="M109" s="12" t="n"/>
-      <c r="N109" s="14" t="n"/>
+      <c r="L109" s="12" t="n"/>
+      <c r="M109" s="13" t="n"/>
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n"/>
@@ -2896,9 +3013,10 @@
       <c r="I110" s="12" t="n"/>
       <c r="J110" s="12" t="n"/>
       <c r="K110" s="12" t="n"/>
-      <c r="L110" s="13" t="n"/>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="14" t="n"/>
+      <c r="L110" s="12" t="n"/>
+      <c r="M110" s="13" t="n"/>
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n"/>
@@ -2915,9 +3033,10 @@
       <c r="I111" s="12" t="n"/>
       <c r="J111" s="12" t="n"/>
       <c r="K111" s="12" t="n"/>
-      <c r="L111" s="13" t="n"/>
-      <c r="M111" s="12" t="n"/>
-      <c r="N111" s="14" t="n"/>
+      <c r="L111" s="12" t="n"/>
+      <c r="M111" s="13" t="n"/>
+      <c r="N111" s="12" t="n"/>
+      <c r="O111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n"/>
@@ -2934,9 +3053,10 @@
       <c r="I112" s="12" t="n"/>
       <c r="J112" s="12" t="n"/>
       <c r="K112" s="12" t="n"/>
-      <c r="L112" s="13" t="n"/>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="14" t="n"/>
+      <c r="L112" s="12" t="n"/>
+      <c r="M112" s="13" t="n"/>
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="n"/>
@@ -2953,9 +3073,10 @@
       <c r="I113" s="12" t="n"/>
       <c r="J113" s="12" t="n"/>
       <c r="K113" s="12" t="n"/>
-      <c r="L113" s="13" t="n"/>
-      <c r="M113" s="12" t="n"/>
-      <c r="N113" s="14" t="n"/>
+      <c r="L113" s="12" t="n"/>
+      <c r="M113" s="13" t="n"/>
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n"/>
@@ -2972,9 +3093,10 @@
       <c r="I114" s="12" t="n"/>
       <c r="J114" s="12" t="n"/>
       <c r="K114" s="12" t="n"/>
-      <c r="L114" s="13" t="n"/>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="14" t="n"/>
+      <c r="L114" s="12" t="n"/>
+      <c r="M114" s="13" t="n"/>
+      <c r="N114" s="12" t="n"/>
+      <c r="O114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n"/>
@@ -2991,9 +3113,10 @@
       <c r="I115" s="12" t="n"/>
       <c r="J115" s="12" t="n"/>
       <c r="K115" s="12" t="n"/>
-      <c r="L115" s="13" t="n"/>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="14" t="n"/>
+      <c r="L115" s="12" t="n"/>
+      <c r="M115" s="13" t="n"/>
+      <c r="N115" s="12" t="n"/>
+      <c r="O115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n"/>
@@ -3010,9 +3133,10 @@
       <c r="I116" s="12" t="n"/>
       <c r="J116" s="12" t="n"/>
       <c r="K116" s="12" t="n"/>
-      <c r="L116" s="13" t="n"/>
-      <c r="M116" s="12" t="n"/>
-      <c r="N116" s="14" t="n"/>
+      <c r="L116" s="12" t="n"/>
+      <c r="M116" s="13" t="n"/>
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n"/>
@@ -3029,9 +3153,10 @@
       <c r="I117" s="12" t="n"/>
       <c r="J117" s="12" t="n"/>
       <c r="K117" s="12" t="n"/>
-      <c r="L117" s="13" t="n"/>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="14" t="n"/>
+      <c r="L117" s="12" t="n"/>
+      <c r="M117" s="13" t="n"/>
+      <c r="N117" s="12" t="n"/>
+      <c r="O117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n"/>
@@ -3048,9 +3173,10 @@
       <c r="I118" s="12" t="n"/>
       <c r="J118" s="12" t="n"/>
       <c r="K118" s="12" t="n"/>
-      <c r="L118" s="13" t="n"/>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="14" t="n"/>
+      <c r="L118" s="12" t="n"/>
+      <c r="M118" s="13" t="n"/>
+      <c r="N118" s="12" t="n"/>
+      <c r="O118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n"/>
@@ -3067,9 +3193,10 @@
       <c r="I119" s="12" t="n"/>
       <c r="J119" s="12" t="n"/>
       <c r="K119" s="12" t="n"/>
-      <c r="L119" s="13" t="n"/>
-      <c r="M119" s="12" t="n"/>
-      <c r="N119" s="14" t="n"/>
+      <c r="L119" s="12" t="n"/>
+      <c r="M119" s="13" t="n"/>
+      <c r="N119" s="12" t="n"/>
+      <c r="O119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n"/>
@@ -3086,9 +3213,10 @@
       <c r="I120" s="12" t="n"/>
       <c r="J120" s="12" t="n"/>
       <c r="K120" s="12" t="n"/>
-      <c r="L120" s="13" t="n"/>
-      <c r="M120" s="12" t="n"/>
-      <c r="N120" s="14" t="n"/>
+      <c r="L120" s="12" t="n"/>
+      <c r="M120" s="13" t="n"/>
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n"/>
@@ -3105,9 +3233,10 @@
       <c r="I121" s="12" t="n"/>
       <c r="J121" s="12" t="n"/>
       <c r="K121" s="12" t="n"/>
-      <c r="L121" s="13" t="n"/>
-      <c r="M121" s="12" t="n"/>
-      <c r="N121" s="14" t="n"/>
+      <c r="L121" s="12" t="n"/>
+      <c r="M121" s="13" t="n"/>
+      <c r="N121" s="12" t="n"/>
+      <c r="O121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n"/>
@@ -3124,9 +3253,10 @@
       <c r="I122" s="12" t="n"/>
       <c r="J122" s="12" t="n"/>
       <c r="K122" s="12" t="n"/>
-      <c r="L122" s="13" t="n"/>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="14" t="n"/>
+      <c r="L122" s="12" t="n"/>
+      <c r="M122" s="13" t="n"/>
+      <c r="N122" s="12" t="n"/>
+      <c r="O122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n"/>
@@ -3143,9 +3273,10 @@
       <c r="I123" s="12" t="n"/>
       <c r="J123" s="12" t="n"/>
       <c r="K123" s="12" t="n"/>
-      <c r="L123" s="13" t="n"/>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="14" t="n"/>
+      <c r="L123" s="12" t="n"/>
+      <c r="M123" s="13" t="n"/>
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n"/>
@@ -3162,9 +3293,10 @@
       <c r="I124" s="12" t="n"/>
       <c r="J124" s="12" t="n"/>
       <c r="K124" s="12" t="n"/>
-      <c r="L124" s="13" t="n"/>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="14" t="n"/>
+      <c r="L124" s="12" t="n"/>
+      <c r="M124" s="13" t="n"/>
+      <c r="N124" s="12" t="n"/>
+      <c r="O124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="n"/>
@@ -3181,9 +3313,10 @@
       <c r="I125" s="12" t="n"/>
       <c r="J125" s="12" t="n"/>
       <c r="K125" s="12" t="n"/>
-      <c r="L125" s="13" t="n"/>
-      <c r="M125" s="12" t="n"/>
-      <c r="N125" s="14" t="n"/>
+      <c r="L125" s="12" t="n"/>
+      <c r="M125" s="13" t="n"/>
+      <c r="N125" s="12" t="n"/>
+      <c r="O125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n"/>
@@ -3200,9 +3333,10 @@
       <c r="I126" s="12" t="n"/>
       <c r="J126" s="12" t="n"/>
       <c r="K126" s="12" t="n"/>
-      <c r="L126" s="13" t="n"/>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="14" t="n"/>
+      <c r="L126" s="12" t="n"/>
+      <c r="M126" s="13" t="n"/>
+      <c r="N126" s="12" t="n"/>
+      <c r="O126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n"/>
@@ -3219,9 +3353,10 @@
       <c r="I127" s="12" t="n"/>
       <c r="J127" s="12" t="n"/>
       <c r="K127" s="12" t="n"/>
-      <c r="L127" s="13" t="n"/>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="14" t="n"/>
+      <c r="L127" s="12" t="n"/>
+      <c r="M127" s="13" t="n"/>
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n"/>
@@ -3238,9 +3373,10 @@
       <c r="I128" s="12" t="n"/>
       <c r="J128" s="12" t="n"/>
       <c r="K128" s="12" t="n"/>
-      <c r="L128" s="13" t="n"/>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="14" t="n"/>
+      <c r="L128" s="12" t="n"/>
+      <c r="M128" s="13" t="n"/>
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n"/>
@@ -3257,9 +3393,10 @@
       <c r="I129" s="12" t="n"/>
       <c r="J129" s="12" t="n"/>
       <c r="K129" s="12" t="n"/>
-      <c r="L129" s="13" t="n"/>
-      <c r="M129" s="12" t="n"/>
-      <c r="N129" s="14" t="n"/>
+      <c r="L129" s="12" t="n"/>
+      <c r="M129" s="13" t="n"/>
+      <c r="N129" s="12" t="n"/>
+      <c r="O129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n"/>
@@ -3276,9 +3413,10 @@
       <c r="I130" s="12" t="n"/>
       <c r="J130" s="12" t="n"/>
       <c r="K130" s="12" t="n"/>
-      <c r="L130" s="13" t="n"/>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="14" t="n"/>
+      <c r="L130" s="12" t="n"/>
+      <c r="M130" s="13" t="n"/>
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n"/>
@@ -3295,9 +3433,10 @@
       <c r="I131" s="12" t="n"/>
       <c r="J131" s="12" t="n"/>
       <c r="K131" s="12" t="n"/>
-      <c r="L131" s="13" t="n"/>
-      <c r="M131" s="12" t="n"/>
-      <c r="N131" s="14" t="n"/>
+      <c r="L131" s="12" t="n"/>
+      <c r="M131" s="13" t="n"/>
+      <c r="N131" s="12" t="n"/>
+      <c r="O131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n"/>
@@ -3314,9 +3453,10 @@
       <c r="I132" s="12" t="n"/>
       <c r="J132" s="12" t="n"/>
       <c r="K132" s="12" t="n"/>
-      <c r="L132" s="13" t="n"/>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="14" t="n"/>
+      <c r="L132" s="12" t="n"/>
+      <c r="M132" s="13" t="n"/>
+      <c r="N132" s="12" t="n"/>
+      <c r="O132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n"/>
@@ -3333,9 +3473,10 @@
       <c r="I133" s="12" t="n"/>
       <c r="J133" s="12" t="n"/>
       <c r="K133" s="12" t="n"/>
-      <c r="L133" s="13" t="n"/>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="14" t="n"/>
+      <c r="L133" s="12" t="n"/>
+      <c r="M133" s="13" t="n"/>
+      <c r="N133" s="12" t="n"/>
+      <c r="O133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n"/>
@@ -3352,9 +3493,10 @@
       <c r="I134" s="12" t="n"/>
       <c r="J134" s="12" t="n"/>
       <c r="K134" s="12" t="n"/>
-      <c r="L134" s="13" t="n"/>
-      <c r="M134" s="12" t="n"/>
-      <c r="N134" s="14" t="n"/>
+      <c r="L134" s="12" t="n"/>
+      <c r="M134" s="13" t="n"/>
+      <c r="N134" s="12" t="n"/>
+      <c r="O134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n"/>
@@ -3371,9 +3513,10 @@
       <c r="I135" s="12" t="n"/>
       <c r="J135" s="12" t="n"/>
       <c r="K135" s="12" t="n"/>
-      <c r="L135" s="13" t="n"/>
-      <c r="M135" s="12" t="n"/>
-      <c r="N135" s="14" t="n"/>
+      <c r="L135" s="12" t="n"/>
+      <c r="M135" s="13" t="n"/>
+      <c r="N135" s="12" t="n"/>
+      <c r="O135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n"/>
@@ -3390,9 +3533,10 @@
       <c r="I136" s="12" t="n"/>
       <c r="J136" s="12" t="n"/>
       <c r="K136" s="12" t="n"/>
-      <c r="L136" s="13" t="n"/>
-      <c r="M136" s="12" t="n"/>
-      <c r="N136" s="14" t="n"/>
+      <c r="L136" s="12" t="n"/>
+      <c r="M136" s="13" t="n"/>
+      <c r="N136" s="12" t="n"/>
+      <c r="O136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="n"/>
@@ -3409,9 +3553,10 @@
       <c r="I137" s="12" t="n"/>
       <c r="J137" s="12" t="n"/>
       <c r="K137" s="12" t="n"/>
-      <c r="L137" s="13" t="n"/>
-      <c r="M137" s="12" t="n"/>
-      <c r="N137" s="14" t="n"/>
+      <c r="L137" s="12" t="n"/>
+      <c r="M137" s="13" t="n"/>
+      <c r="N137" s="12" t="n"/>
+      <c r="O137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="n"/>
@@ -3428,9 +3573,10 @@
       <c r="I138" s="12" t="n"/>
       <c r="J138" s="12" t="n"/>
       <c r="K138" s="12" t="n"/>
-      <c r="L138" s="13" t="n"/>
-      <c r="M138" s="12" t="n"/>
-      <c r="N138" s="14" t="n"/>
+      <c r="L138" s="12" t="n"/>
+      <c r="M138" s="13" t="n"/>
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="n"/>
@@ -3447,9 +3593,10 @@
       <c r="I139" s="12" t="n"/>
       <c r="J139" s="12" t="n"/>
       <c r="K139" s="12" t="n"/>
-      <c r="L139" s="13" t="n"/>
-      <c r="M139" s="12" t="n"/>
-      <c r="N139" s="14" t="n"/>
+      <c r="L139" s="12" t="n"/>
+      <c r="M139" s="13" t="n"/>
+      <c r="N139" s="12" t="n"/>
+      <c r="O139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="n"/>
@@ -3466,9 +3613,10 @@
       <c r="I140" s="12" t="n"/>
       <c r="J140" s="12" t="n"/>
       <c r="K140" s="12" t="n"/>
-      <c r="L140" s="13" t="n"/>
-      <c r="M140" s="12" t="n"/>
-      <c r="N140" s="14" t="n"/>
+      <c r="L140" s="12" t="n"/>
+      <c r="M140" s="13" t="n"/>
+      <c r="N140" s="12" t="n"/>
+      <c r="O140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="n"/>
@@ -3485,9 +3633,10 @@
       <c r="I141" s="12" t="n"/>
       <c r="J141" s="12" t="n"/>
       <c r="K141" s="12" t="n"/>
-      <c r="L141" s="13" t="n"/>
-      <c r="M141" s="12" t="n"/>
-      <c r="N141" s="14" t="n"/>
+      <c r="L141" s="12" t="n"/>
+      <c r="M141" s="13" t="n"/>
+      <c r="N141" s="12" t="n"/>
+      <c r="O141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="n"/>
@@ -3504,9 +3653,10 @@
       <c r="I142" s="12" t="n"/>
       <c r="J142" s="12" t="n"/>
       <c r="K142" s="12" t="n"/>
-      <c r="L142" s="13" t="n"/>
-      <c r="M142" s="12" t="n"/>
-      <c r="N142" s="14" t="n"/>
+      <c r="L142" s="12" t="n"/>
+      <c r="M142" s="13" t="n"/>
+      <c r="N142" s="12" t="n"/>
+      <c r="O142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="n"/>
@@ -3523,9 +3673,10 @@
       <c r="I143" s="12" t="n"/>
       <c r="J143" s="12" t="n"/>
       <c r="K143" s="12" t="n"/>
-      <c r="L143" s="13" t="n"/>
-      <c r="M143" s="12" t="n"/>
-      <c r="N143" s="14" t="n"/>
+      <c r="L143" s="12" t="n"/>
+      <c r="M143" s="13" t="n"/>
+      <c r="N143" s="12" t="n"/>
+      <c r="O143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="n"/>
@@ -3542,9 +3693,10 @@
       <c r="I144" s="12" t="n"/>
       <c r="J144" s="12" t="n"/>
       <c r="K144" s="12" t="n"/>
-      <c r="L144" s="13" t="n"/>
-      <c r="M144" s="12" t="n"/>
-      <c r="N144" s="14" t="n"/>
+      <c r="L144" s="12" t="n"/>
+      <c r="M144" s="13" t="n"/>
+      <c r="N144" s="12" t="n"/>
+      <c r="O144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="n"/>
@@ -3561,9 +3713,10 @@
       <c r="I145" s="12" t="n"/>
       <c r="J145" s="12" t="n"/>
       <c r="K145" s="12" t="n"/>
-      <c r="L145" s="13" t="n"/>
-      <c r="M145" s="12" t="n"/>
-      <c r="N145" s="14" t="n"/>
+      <c r="L145" s="12" t="n"/>
+      <c r="M145" s="13" t="n"/>
+      <c r="N145" s="12" t="n"/>
+      <c r="O145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="n"/>
@@ -3580,9 +3733,10 @@
       <c r="I146" s="12" t="n"/>
       <c r="J146" s="12" t="n"/>
       <c r="K146" s="12" t="n"/>
-      <c r="L146" s="13" t="n"/>
-      <c r="M146" s="12" t="n"/>
-      <c r="N146" s="14" t="n"/>
+      <c r="L146" s="12" t="n"/>
+      <c r="M146" s="13" t="n"/>
+      <c r="N146" s="12" t="n"/>
+      <c r="O146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="n"/>
@@ -3599,9 +3753,10 @@
       <c r="I147" s="12" t="n"/>
       <c r="J147" s="12" t="n"/>
       <c r="K147" s="12" t="n"/>
-      <c r="L147" s="13" t="n"/>
-      <c r="M147" s="12" t="n"/>
-      <c r="N147" s="14" t="n"/>
+      <c r="L147" s="12" t="n"/>
+      <c r="M147" s="13" t="n"/>
+      <c r="N147" s="12" t="n"/>
+      <c r="O147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="n"/>
@@ -3618,9 +3773,10 @@
       <c r="I148" s="12" t="n"/>
       <c r="J148" s="12" t="n"/>
       <c r="K148" s="12" t="n"/>
-      <c r="L148" s="13" t="n"/>
-      <c r="M148" s="12" t="n"/>
-      <c r="N148" s="14" t="n"/>
+      <c r="L148" s="12" t="n"/>
+      <c r="M148" s="13" t="n"/>
+      <c r="N148" s="12" t="n"/>
+      <c r="O148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="n"/>
@@ -3637,9 +3793,10 @@
       <c r="I149" s="12" t="n"/>
       <c r="J149" s="12" t="n"/>
       <c r="K149" s="12" t="n"/>
-      <c r="L149" s="13" t="n"/>
-      <c r="M149" s="12" t="n"/>
-      <c r="N149" s="14" t="n"/>
+      <c r="L149" s="12" t="n"/>
+      <c r="M149" s="13" t="n"/>
+      <c r="N149" s="12" t="n"/>
+      <c r="O149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="n"/>
@@ -3656,9 +3813,10 @@
       <c r="I150" s="12" t="n"/>
       <c r="J150" s="12" t="n"/>
       <c r="K150" s="12" t="n"/>
-      <c r="L150" s="13" t="n"/>
-      <c r="M150" s="12" t="n"/>
-      <c r="N150" s="14" t="n"/>
+      <c r="L150" s="12" t="n"/>
+      <c r="M150" s="13" t="n"/>
+      <c r="N150" s="12" t="n"/>
+      <c r="O150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="n"/>
@@ -3675,9 +3833,10 @@
       <c r="I151" s="12" t="n"/>
       <c r="J151" s="12" t="n"/>
       <c r="K151" s="12" t="n"/>
-      <c r="L151" s="13" t="n"/>
-      <c r="M151" s="12" t="n"/>
-      <c r="N151" s="14" t="n"/>
+      <c r="L151" s="12" t="n"/>
+      <c r="M151" s="13" t="n"/>
+      <c r="N151" s="12" t="n"/>
+      <c r="O151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="n"/>
@@ -3694,9 +3853,10 @@
       <c r="I152" s="12" t="n"/>
       <c r="J152" s="12" t="n"/>
       <c r="K152" s="12" t="n"/>
-      <c r="L152" s="13" t="n"/>
-      <c r="M152" s="12" t="n"/>
-      <c r="N152" s="14" t="n"/>
+      <c r="L152" s="12" t="n"/>
+      <c r="M152" s="13" t="n"/>
+      <c r="N152" s="12" t="n"/>
+      <c r="O152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="n"/>
@@ -3713,9 +3873,10 @@
       <c r="I153" s="12" t="n"/>
       <c r="J153" s="12" t="n"/>
       <c r="K153" s="12" t="n"/>
-      <c r="L153" s="13" t="n"/>
-      <c r="M153" s="12" t="n"/>
-      <c r="N153" s="14" t="n"/>
+      <c r="L153" s="12" t="n"/>
+      <c r="M153" s="13" t="n"/>
+      <c r="N153" s="12" t="n"/>
+      <c r="O153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="n"/>
@@ -3732,9 +3893,10 @@
       <c r="I154" s="12" t="n"/>
       <c r="J154" s="12" t="n"/>
       <c r="K154" s="12" t="n"/>
-      <c r="L154" s="13" t="n"/>
-      <c r="M154" s="12" t="n"/>
-      <c r="N154" s="14" t="n"/>
+      <c r="L154" s="12" t="n"/>
+      <c r="M154" s="13" t="n"/>
+      <c r="N154" s="12" t="n"/>
+      <c r="O154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n"/>
@@ -3751,9 +3913,10 @@
       <c r="I155" s="12" t="n"/>
       <c r="J155" s="12" t="n"/>
       <c r="K155" s="12" t="n"/>
-      <c r="L155" s="13" t="n"/>
-      <c r="M155" s="12" t="n"/>
-      <c r="N155" s="14" t="n"/>
+      <c r="L155" s="12" t="n"/>
+      <c r="M155" s="13" t="n"/>
+      <c r="N155" s="12" t="n"/>
+      <c r="O155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="n"/>
@@ -3770,9 +3933,10 @@
       <c r="I156" s="12" t="n"/>
       <c r="J156" s="12" t="n"/>
       <c r="K156" s="12" t="n"/>
-      <c r="L156" s="13" t="n"/>
-      <c r="M156" s="12" t="n"/>
-      <c r="N156" s="14" t="n"/>
+      <c r="L156" s="12" t="n"/>
+      <c r="M156" s="13" t="n"/>
+      <c r="N156" s="12" t="n"/>
+      <c r="O156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="n"/>
@@ -3789,9 +3953,10 @@
       <c r="I157" s="12" t="n"/>
       <c r="J157" s="12" t="n"/>
       <c r="K157" s="12" t="n"/>
-      <c r="L157" s="13" t="n"/>
-      <c r="M157" s="12" t="n"/>
-      <c r="N157" s="14" t="n"/>
+      <c r="L157" s="12" t="n"/>
+      <c r="M157" s="13" t="n"/>
+      <c r="N157" s="12" t="n"/>
+      <c r="O157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="n"/>
@@ -3808,9 +3973,10 @@
       <c r="I158" s="12" t="n"/>
       <c r="J158" s="12" t="n"/>
       <c r="K158" s="12" t="n"/>
-      <c r="L158" s="13" t="n"/>
-      <c r="M158" s="12" t="n"/>
-      <c r="N158" s="14" t="n"/>
+      <c r="L158" s="12" t="n"/>
+      <c r="M158" s="13" t="n"/>
+      <c r="N158" s="12" t="n"/>
+      <c r="O158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="n"/>
@@ -3827,9 +3993,10 @@
       <c r="I159" s="12" t="n"/>
       <c r="J159" s="12" t="n"/>
       <c r="K159" s="12" t="n"/>
-      <c r="L159" s="13" t="n"/>
-      <c r="M159" s="12" t="n"/>
-      <c r="N159" s="14" t="n"/>
+      <c r="L159" s="12" t="n"/>
+      <c r="M159" s="13" t="n"/>
+      <c r="N159" s="12" t="n"/>
+      <c r="O159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="n"/>
@@ -3846,9 +4013,10 @@
       <c r="I160" s="12" t="n"/>
       <c r="J160" s="12" t="n"/>
       <c r="K160" s="12" t="n"/>
-      <c r="L160" s="13" t="n"/>
-      <c r="M160" s="12" t="n"/>
-      <c r="N160" s="14" t="n"/>
+      <c r="L160" s="12" t="n"/>
+      <c r="M160" s="13" t="n"/>
+      <c r="N160" s="12" t="n"/>
+      <c r="O160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="n"/>
@@ -3865,9 +4033,10 @@
       <c r="I161" s="12" t="n"/>
       <c r="J161" s="12" t="n"/>
       <c r="K161" s="12" t="n"/>
-      <c r="L161" s="13" t="n"/>
-      <c r="M161" s="12" t="n"/>
-      <c r="N161" s="14" t="n"/>
+      <c r="L161" s="12" t="n"/>
+      <c r="M161" s="13" t="n"/>
+      <c r="N161" s="12" t="n"/>
+      <c r="O161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="n"/>
@@ -3884,9 +4053,10 @@
       <c r="I162" s="12" t="n"/>
       <c r="J162" s="12" t="n"/>
       <c r="K162" s="12" t="n"/>
-      <c r="L162" s="13" t="n"/>
-      <c r="M162" s="12" t="n"/>
-      <c r="N162" s="14" t="n"/>
+      <c r="L162" s="12" t="n"/>
+      <c r="M162" s="13" t="n"/>
+      <c r="N162" s="12" t="n"/>
+      <c r="O162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="n"/>
@@ -3903,9 +4073,10 @@
       <c r="I163" s="12" t="n"/>
       <c r="J163" s="12" t="n"/>
       <c r="K163" s="12" t="n"/>
-      <c r="L163" s="13" t="n"/>
-      <c r="M163" s="12" t="n"/>
-      <c r="N163" s="14" t="n"/>
+      <c r="L163" s="12" t="n"/>
+      <c r="M163" s="13" t="n"/>
+      <c r="N163" s="12" t="n"/>
+      <c r="O163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="n"/>
@@ -3922,9 +4093,10 @@
       <c r="I164" s="12" t="n"/>
       <c r="J164" s="12" t="n"/>
       <c r="K164" s="12" t="n"/>
-      <c r="L164" s="13" t="n"/>
-      <c r="M164" s="12" t="n"/>
-      <c r="N164" s="14" t="n"/>
+      <c r="L164" s="12" t="n"/>
+      <c r="M164" s="13" t="n"/>
+      <c r="N164" s="12" t="n"/>
+      <c r="O164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="n"/>
@@ -3941,9 +4113,10 @@
       <c r="I165" s="12" t="n"/>
       <c r="J165" s="12" t="n"/>
       <c r="K165" s="12" t="n"/>
-      <c r="L165" s="13" t="n"/>
-      <c r="M165" s="12" t="n"/>
-      <c r="N165" s="14" t="n"/>
+      <c r="L165" s="12" t="n"/>
+      <c r="M165" s="13" t="n"/>
+      <c r="N165" s="12" t="n"/>
+      <c r="O165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="n"/>
@@ -3960,9 +4133,10 @@
       <c r="I166" s="12" t="n"/>
       <c r="J166" s="12" t="n"/>
       <c r="K166" s="12" t="n"/>
-      <c r="L166" s="13" t="n"/>
-      <c r="M166" s="12" t="n"/>
-      <c r="N166" s="14" t="n"/>
+      <c r="L166" s="12" t="n"/>
+      <c r="M166" s="13" t="n"/>
+      <c r="N166" s="12" t="n"/>
+      <c r="O166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="n"/>
@@ -3979,9 +4153,10 @@
       <c r="I167" s="12" t="n"/>
       <c r="J167" s="12" t="n"/>
       <c r="K167" s="12" t="n"/>
-      <c r="L167" s="13" t="n"/>
-      <c r="M167" s="12" t="n"/>
-      <c r="N167" s="14" t="n"/>
+      <c r="L167" s="12" t="n"/>
+      <c r="M167" s="13" t="n"/>
+      <c r="N167" s="12" t="n"/>
+      <c r="O167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="n"/>
@@ -3998,9 +4173,10 @@
       <c r="I168" s="12" t="n"/>
       <c r="J168" s="12" t="n"/>
       <c r="K168" s="12" t="n"/>
-      <c r="L168" s="13" t="n"/>
-      <c r="M168" s="12" t="n"/>
-      <c r="N168" s="14" t="n"/>
+      <c r="L168" s="12" t="n"/>
+      <c r="M168" s="13" t="n"/>
+      <c r="N168" s="12" t="n"/>
+      <c r="O168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="n"/>
@@ -4017,9 +4193,10 @@
       <c r="I169" s="12" t="n"/>
       <c r="J169" s="12" t="n"/>
       <c r="K169" s="12" t="n"/>
-      <c r="L169" s="13" t="n"/>
-      <c r="M169" s="12" t="n"/>
-      <c r="N169" s="14" t="n"/>
+      <c r="L169" s="12" t="n"/>
+      <c r="M169" s="13" t="n"/>
+      <c r="N169" s="12" t="n"/>
+      <c r="O169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="n"/>
@@ -4036,9 +4213,10 @@
       <c r="I170" s="12" t="n"/>
       <c r="J170" s="12" t="n"/>
       <c r="K170" s="12" t="n"/>
-      <c r="L170" s="13" t="n"/>
-      <c r="M170" s="12" t="n"/>
-      <c r="N170" s="14" t="n"/>
+      <c r="L170" s="12" t="n"/>
+      <c r="M170" s="13" t="n"/>
+      <c r="N170" s="12" t="n"/>
+      <c r="O170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="n"/>
@@ -4055,9 +4233,10 @@
       <c r="I171" s="12" t="n"/>
       <c r="J171" s="12" t="n"/>
       <c r="K171" s="12" t="n"/>
-      <c r="L171" s="13" t="n"/>
-      <c r="M171" s="12" t="n"/>
-      <c r="N171" s="14" t="n"/>
+      <c r="L171" s="12" t="n"/>
+      <c r="M171" s="13" t="n"/>
+      <c r="N171" s="12" t="n"/>
+      <c r="O171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="n"/>
@@ -4074,9 +4253,10 @@
       <c r="I172" s="12" t="n"/>
       <c r="J172" s="12" t="n"/>
       <c r="K172" s="12" t="n"/>
-      <c r="L172" s="13" t="n"/>
-      <c r="M172" s="12" t="n"/>
-      <c r="N172" s="14" t="n"/>
+      <c r="L172" s="12" t="n"/>
+      <c r="M172" s="13" t="n"/>
+      <c r="N172" s="12" t="n"/>
+      <c r="O172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="n"/>
@@ -4093,9 +4273,10 @@
       <c r="I173" s="12" t="n"/>
       <c r="J173" s="12" t="n"/>
       <c r="K173" s="12" t="n"/>
-      <c r="L173" s="13" t="n"/>
-      <c r="M173" s="12" t="n"/>
-      <c r="N173" s="14" t="n"/>
+      <c r="L173" s="12" t="n"/>
+      <c r="M173" s="13" t="n"/>
+      <c r="N173" s="12" t="n"/>
+      <c r="O173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="n"/>
@@ -4112,9 +4293,10 @@
       <c r="I174" s="12" t="n"/>
       <c r="J174" s="12" t="n"/>
       <c r="K174" s="12" t="n"/>
-      <c r="L174" s="13" t="n"/>
-      <c r="M174" s="12" t="n"/>
-      <c r="N174" s="14" t="n"/>
+      <c r="L174" s="12" t="n"/>
+      <c r="M174" s="13" t="n"/>
+      <c r="N174" s="12" t="n"/>
+      <c r="O174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="n"/>
@@ -4131,9 +4313,10 @@
       <c r="I175" s="12" t="n"/>
       <c r="J175" s="12" t="n"/>
       <c r="K175" s="12" t="n"/>
-      <c r="L175" s="13" t="n"/>
-      <c r="M175" s="12" t="n"/>
-      <c r="N175" s="14" t="n"/>
+      <c r="L175" s="12" t="n"/>
+      <c r="M175" s="13" t="n"/>
+      <c r="N175" s="12" t="n"/>
+      <c r="O175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n"/>
@@ -4150,9 +4333,10 @@
       <c r="I176" s="12" t="n"/>
       <c r="J176" s="12" t="n"/>
       <c r="K176" s="12" t="n"/>
-      <c r="L176" s="13" t="n"/>
-      <c r="M176" s="12" t="n"/>
-      <c r="N176" s="14" t="n"/>
+      <c r="L176" s="12" t="n"/>
+      <c r="M176" s="13" t="n"/>
+      <c r="N176" s="12" t="n"/>
+      <c r="O176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n"/>
@@ -4169,9 +4353,10 @@
       <c r="I177" s="12" t="n"/>
       <c r="J177" s="12" t="n"/>
       <c r="K177" s="12" t="n"/>
-      <c r="L177" s="13" t="n"/>
-      <c r="M177" s="12" t="n"/>
-      <c r="N177" s="14" t="n"/>
+      <c r="L177" s="12" t="n"/>
+      <c r="M177" s="13" t="n"/>
+      <c r="N177" s="12" t="n"/>
+      <c r="O177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="n"/>
@@ -4188,9 +4373,10 @@
       <c r="I178" s="12" t="n"/>
       <c r="J178" s="12" t="n"/>
       <c r="K178" s="12" t="n"/>
-      <c r="L178" s="13" t="n"/>
-      <c r="M178" s="12" t="n"/>
-      <c r="N178" s="14" t="n"/>
+      <c r="L178" s="12" t="n"/>
+      <c r="M178" s="13" t="n"/>
+      <c r="N178" s="12" t="n"/>
+      <c r="O178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="n"/>
@@ -4207,9 +4393,10 @@
       <c r="I179" s="12" t="n"/>
       <c r="J179" s="12" t="n"/>
       <c r="K179" s="12" t="n"/>
-      <c r="L179" s="13" t="n"/>
-      <c r="M179" s="12" t="n"/>
-      <c r="N179" s="14" t="n"/>
+      <c r="L179" s="12" t="n"/>
+      <c r="M179" s="13" t="n"/>
+      <c r="N179" s="12" t="n"/>
+      <c r="O179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="n"/>
@@ -4226,9 +4413,10 @@
       <c r="I180" s="12" t="n"/>
       <c r="J180" s="12" t="n"/>
       <c r="K180" s="12" t="n"/>
-      <c r="L180" s="13" t="n"/>
-      <c r="M180" s="12" t="n"/>
-      <c r="N180" s="14" t="n"/>
+      <c r="L180" s="12" t="n"/>
+      <c r="M180" s="13" t="n"/>
+      <c r="N180" s="12" t="n"/>
+      <c r="O180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="n"/>
@@ -4245,9 +4433,10 @@
       <c r="I181" s="12" t="n"/>
       <c r="J181" s="12" t="n"/>
       <c r="K181" s="12" t="n"/>
-      <c r="L181" s="13" t="n"/>
-      <c r="M181" s="12" t="n"/>
-      <c r="N181" s="14" t="n"/>
+      <c r="L181" s="12" t="n"/>
+      <c r="M181" s="13" t="n"/>
+      <c r="N181" s="12" t="n"/>
+      <c r="O181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n"/>
@@ -4264,9 +4453,10 @@
       <c r="I182" s="12" t="n"/>
       <c r="J182" s="12" t="n"/>
       <c r="K182" s="12" t="n"/>
-      <c r="L182" s="13" t="n"/>
-      <c r="M182" s="12" t="n"/>
-      <c r="N182" s="14" t="n"/>
+      <c r="L182" s="12" t="n"/>
+      <c r="M182" s="13" t="n"/>
+      <c r="N182" s="12" t="n"/>
+      <c r="O182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n"/>
@@ -4283,9 +4473,10 @@
       <c r="I183" s="12" t="n"/>
       <c r="J183" s="12" t="n"/>
       <c r="K183" s="12" t="n"/>
-      <c r="L183" s="13" t="n"/>
-      <c r="M183" s="12" t="n"/>
-      <c r="N183" s="14" t="n"/>
+      <c r="L183" s="12" t="n"/>
+      <c r="M183" s="13" t="n"/>
+      <c r="N183" s="12" t="n"/>
+      <c r="O183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="n"/>
@@ -4302,9 +4493,10 @@
       <c r="I184" s="12" t="n"/>
       <c r="J184" s="12" t="n"/>
       <c r="K184" s="12" t="n"/>
-      <c r="L184" s="13" t="n"/>
-      <c r="M184" s="12" t="n"/>
-      <c r="N184" s="14" t="n"/>
+      <c r="L184" s="12" t="n"/>
+      <c r="M184" s="13" t="n"/>
+      <c r="N184" s="12" t="n"/>
+      <c r="O184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="n"/>
@@ -4321,9 +4513,10 @@
       <c r="I185" s="12" t="n"/>
       <c r="J185" s="12" t="n"/>
       <c r="K185" s="12" t="n"/>
-      <c r="L185" s="13" t="n"/>
-      <c r="M185" s="12" t="n"/>
-      <c r="N185" s="14" t="n"/>
+      <c r="L185" s="12" t="n"/>
+      <c r="M185" s="13" t="n"/>
+      <c r="N185" s="12" t="n"/>
+      <c r="O185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="n"/>
@@ -4340,9 +4533,10 @@
       <c r="I186" s="12" t="n"/>
       <c r="J186" s="12" t="n"/>
       <c r="K186" s="12" t="n"/>
-      <c r="L186" s="13" t="n"/>
-      <c r="M186" s="12" t="n"/>
-      <c r="N186" s="14" t="n"/>
+      <c r="L186" s="12" t="n"/>
+      <c r="M186" s="13" t="n"/>
+      <c r="N186" s="12" t="n"/>
+      <c r="O186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="n"/>
@@ -4359,9 +4553,10 @@
       <c r="I187" s="12" t="n"/>
       <c r="J187" s="12" t="n"/>
       <c r="K187" s="12" t="n"/>
-      <c r="L187" s="13" t="n"/>
-      <c r="M187" s="12" t="n"/>
-      <c r="N187" s="14" t="n"/>
+      <c r="L187" s="12" t="n"/>
+      <c r="M187" s="13" t="n"/>
+      <c r="N187" s="12" t="n"/>
+      <c r="O187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="n"/>
@@ -4378,9 +4573,10 @@
       <c r="I188" s="12" t="n"/>
       <c r="J188" s="12" t="n"/>
       <c r="K188" s="12" t="n"/>
-      <c r="L188" s="13" t="n"/>
-      <c r="M188" s="12" t="n"/>
-      <c r="N188" s="14" t="n"/>
+      <c r="L188" s="12" t="n"/>
+      <c r="M188" s="13" t="n"/>
+      <c r="N188" s="12" t="n"/>
+      <c r="O188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="n"/>
@@ -4397,9 +4593,10 @@
       <c r="I189" s="12" t="n"/>
       <c r="J189" s="12" t="n"/>
       <c r="K189" s="12" t="n"/>
-      <c r="L189" s="13" t="n"/>
-      <c r="M189" s="12" t="n"/>
-      <c r="N189" s="14" t="n"/>
+      <c r="L189" s="12" t="n"/>
+      <c r="M189" s="13" t="n"/>
+      <c r="N189" s="12" t="n"/>
+      <c r="O189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="n"/>
@@ -4416,9 +4613,10 @@
       <c r="I190" s="12" t="n"/>
       <c r="J190" s="12" t="n"/>
       <c r="K190" s="12" t="n"/>
-      <c r="L190" s="13" t="n"/>
-      <c r="M190" s="12" t="n"/>
-      <c r="N190" s="14" t="n"/>
+      <c r="L190" s="12" t="n"/>
+      <c r="M190" s="13" t="n"/>
+      <c r="N190" s="12" t="n"/>
+      <c r="O190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="n"/>
@@ -4435,9 +4633,10 @@
       <c r="I191" s="12" t="n"/>
       <c r="J191" s="12" t="n"/>
       <c r="K191" s="12" t="n"/>
-      <c r="L191" s="13" t="n"/>
-      <c r="M191" s="12" t="n"/>
-      <c r="N191" s="14" t="n"/>
+      <c r="L191" s="12" t="n"/>
+      <c r="M191" s="13" t="n"/>
+      <c r="N191" s="12" t="n"/>
+      <c r="O191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="n"/>
@@ -4454,9 +4653,10 @@
       <c r="I192" s="12" t="n"/>
       <c r="J192" s="12" t="n"/>
       <c r="K192" s="12" t="n"/>
-      <c r="L192" s="13" t="n"/>
-      <c r="M192" s="12" t="n"/>
-      <c r="N192" s="14" t="n"/>
+      <c r="L192" s="12" t="n"/>
+      <c r="M192" s="13" t="n"/>
+      <c r="N192" s="12" t="n"/>
+      <c r="O192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="n"/>
@@ -4473,9 +4673,10 @@
       <c r="I193" s="12" t="n"/>
       <c r="J193" s="12" t="n"/>
       <c r="K193" s="12" t="n"/>
-      <c r="L193" s="13" t="n"/>
-      <c r="M193" s="12" t="n"/>
-      <c r="N193" s="14" t="n"/>
+      <c r="L193" s="12" t="n"/>
+      <c r="M193" s="13" t="n"/>
+      <c r="N193" s="12" t="n"/>
+      <c r="O193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="n"/>
@@ -4492,9 +4693,10 @@
       <c r="I194" s="12" t="n"/>
       <c r="J194" s="12" t="n"/>
       <c r="K194" s="12" t="n"/>
-      <c r="L194" s="13" t="n"/>
-      <c r="M194" s="12" t="n"/>
-      <c r="N194" s="14" t="n"/>
+      <c r="L194" s="12" t="n"/>
+      <c r="M194" s="13" t="n"/>
+      <c r="N194" s="12" t="n"/>
+      <c r="O194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="n"/>
@@ -4511,9 +4713,10 @@
       <c r="I195" s="12" t="n"/>
       <c r="J195" s="12" t="n"/>
       <c r="K195" s="12" t="n"/>
-      <c r="L195" s="13" t="n"/>
-      <c r="M195" s="12" t="n"/>
-      <c r="N195" s="14" t="n"/>
+      <c r="L195" s="12" t="n"/>
+      <c r="M195" s="13" t="n"/>
+      <c r="N195" s="12" t="n"/>
+      <c r="O195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="n"/>
@@ -4530,9 +4733,10 @@
       <c r="I196" s="12" t="n"/>
       <c r="J196" s="12" t="n"/>
       <c r="K196" s="12" t="n"/>
-      <c r="L196" s="13" t="n"/>
-      <c r="M196" s="12" t="n"/>
-      <c r="N196" s="14" t="n"/>
+      <c r="L196" s="12" t="n"/>
+      <c r="M196" s="13" t="n"/>
+      <c r="N196" s="12" t="n"/>
+      <c r="O196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="12" t="n"/>
@@ -4549,9 +4753,10 @@
       <c r="I197" s="12" t="n"/>
       <c r="J197" s="12" t="n"/>
       <c r="K197" s="12" t="n"/>
-      <c r="L197" s="13" t="n"/>
-      <c r="M197" s="12" t="n"/>
-      <c r="N197" s="14" t="n"/>
+      <c r="L197" s="12" t="n"/>
+      <c r="M197" s="13" t="n"/>
+      <c r="N197" s="12" t="n"/>
+      <c r="O197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="n"/>
@@ -4568,9 +4773,10 @@
       <c r="I198" s="12" t="n"/>
       <c r="J198" s="12" t="n"/>
       <c r="K198" s="12" t="n"/>
-      <c r="L198" s="13" t="n"/>
-      <c r="M198" s="12" t="n"/>
-      <c r="N198" s="14" t="n"/>
+      <c r="L198" s="12" t="n"/>
+      <c r="M198" s="13" t="n"/>
+      <c r="N198" s="12" t="n"/>
+      <c r="O198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="n"/>
@@ -4587,9 +4793,10 @@
       <c r="I199" s="12" t="n"/>
       <c r="J199" s="12" t="n"/>
       <c r="K199" s="12" t="n"/>
-      <c r="L199" s="13" t="n"/>
-      <c r="M199" s="12" t="n"/>
-      <c r="N199" s="14" t="n"/>
+      <c r="L199" s="12" t="n"/>
+      <c r="M199" s="13" t="n"/>
+      <c r="N199" s="12" t="n"/>
+      <c r="O199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="n"/>
@@ -4606,9 +4813,10 @@
       <c r="I200" s="12" t="n"/>
       <c r="J200" s="12" t="n"/>
       <c r="K200" s="12" t="n"/>
-      <c r="L200" s="13" t="n"/>
-      <c r="M200" s="12" t="n"/>
-      <c r="N200" s="14" t="n"/>
+      <c r="L200" s="12" t="n"/>
+      <c r="M200" s="13" t="n"/>
+      <c r="N200" s="12" t="n"/>
+      <c r="O200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="n"/>
@@ -4625,42 +4833,47 @@
       <c r="I201" s="12" t="n"/>
       <c r="J201" s="12" t="n"/>
       <c r="K201" s="12" t="n"/>
-      <c r="L201" s="13" t="n"/>
-      <c r="M201" s="12" t="n"/>
-      <c r="N201" s="14" t="n"/>
+      <c r="L201" s="12" t="n"/>
+      <c r="M201" s="13" t="n"/>
+      <c r="N201" s="12" t="n"/>
+      <c r="O201" s="14" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation sqref="C2:C201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
       <formula1>=選單!$A$1:$A$24</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
       <formula1>=選單!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
+    <dataValidation sqref="L2:L201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請從下拉選單選擇" type="list">
       <formula1>=選單!$G$1:$G$2</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
+    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 1000 的整數" type="whole" operator="between">
       <formula1>0</formula1>
-      <formula2>100</formula2>
+      <formula2>1000</formula2>
     </dataValidation>
     <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 200 的整數" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
+    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 200 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 1000 的整數" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000</formula2>
+    </dataValidation>
+    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 100 的整數" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation sqref="M2:M201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 300 的整數" type="whole" operator="between">
+    <dataValidation sqref="N2:N201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="請填 0 到 300 的整數" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
@@ -10329,7 +10542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10541,12 +10754,12 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>武功每升一級，給「武術造詣」= 新等級 × 係數。（龍圖心經用的是 10）</t>
+          <t>武功每升一級，給「武術造詣」= 新等級 × 係數。（龍圖心經用 10；三門刀法定案 100）</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
+          <t>0～1000</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -10590,17 +10803,17 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>武學之道係數</t>
+          <t>武學之道減數</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>給「武學之道」=（新等級 − 起始等級 + 1）× 係數。</t>
+          <t>公式裡要減掉的數字，見下一欄。</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
+          <t>0～200</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -10608,59 +10821,55 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>有（龍圖心經）</t>
-        </is>
-      </c>
+      <c r="E11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>武學之道係數</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>給「武學之道」=（新等級 − 減數）× 係數。（龍圖心經：起始 51、減數 41、係數 10；三門刀法定案：起始 30、減數 11、係數 75）</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>0～1000</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>有（龍圖心經）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>整套特效</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>整套武功共有的特殊效果。
 「三招重演」（三門刀法）：最近三招都命中時，有機會立即把這三招再使一次；重演必中（不會被閃開或格開，防具照樣減傷），重演的招不算連中，發動後連中紀錄歸零。</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>下拉選單</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>無</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>整套特效機率</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>條件達成時發動的基本機率。三招重演另加「天生膽識÷4」（小數捨去，不含裝備），寫在備註。</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>0～100</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -10672,78 +10881,82 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
+          <t>整套特效機率</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>條件達成時發動的基本機率。三招重演另加「天生膽識÷4」（小數捨去，不含裝備），寫在備註。</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>0～100</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
           <t>整套特效強度</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>三招重演：重演那三招的傷害 %，以那招平常的傷害（含各種加成）為準，100 = 和平常一樣。</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>0～300</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>【招式表】</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr"/>
-      <c r="C15" s="18" t="inlineStr"/>
-      <c r="D15" s="18" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>武功代號</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>這一招屬於哪套武功，從「武功總表」已建立的代號中選。</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>下拉選單</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>（必填）</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr"/>
+      <c r="C16" s="18" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr"/>
+      <c r="E16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>順序</t>
+          <t>武功代號</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>招式的編號，用來對應第一部分寫的招式敘述。</t>
+          <t>這一招屬於哪套武功，從「武功總表」已建立的代號中選。</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>1～30</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -10756,17 +10969,17 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>招式名</t>
+          <t>順序</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>例如「三門齊開」。不用加「」。</t>
+          <t>招式的編號，用來對應第一部分寫的招式敘述。</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>中文</t>
+          <t>1～30</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -10774,75 +10987,71 @@
           <t>（必填）</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
+      <c r="E18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>解鎖等級</t>
+          <t>招式名</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>武功練到幾級才會使出這一招。</t>
+          <t>例如「三門齊開」。不用加「」。</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>0～200</t>
+          <t>中文</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>0（一開始就會）</t>
+          <t>（必填）</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>命中加成</t>
+          <t>解鎖等級</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>加在命中判定上。越高越容易打中。程式欄位 attack。</t>
+          <t>武功練到幾級才會使出這一招。</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>-30～30</t>
+          <t>0～200</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0（一開始就會）</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>防守加成</t>
+          <t>命中加成</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>出這招後，對手下一招比較難打中你。程式欄位 defense。</t>
+          <t>加在命中判定上。越高越容易打中。程式欄位 attack。</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
@@ -10864,12 +11073,12 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>內力加成</t>
+          <t>防守加成</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>有運內功時，額外增加的內力力道。程式欄位 force。</t>
+          <t>出這招後，對手下一招比較難打中你。程式欄位 defense。</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
@@ -10891,17 +11100,17 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>招式傷害加成</t>
+          <t>內力加成</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>這一招自己的傷害加成，會和整套加成相加。可以填負數，代表這招傷害比較低（例如防守招）。</t>
+          <t>有運內功時，額外增加的內力力道。程式欄位 force。</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>-50～100</t>
+          <t>-30～30</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -10911,65 +11120,65 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>總傷害加成</t>
+          <t>招式傷害加成</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>自動計算 = 整套加成 + 招式加成。</t>
+          <t>這一招自己的傷害加成，會和整套加成相加。可以填負數，代表這招傷害比較低（例如防守招）。</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>（自動）</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr"/>
-      <c r="E24" s="19" t="inlineStr"/>
+          <t>-50～100</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>傷害類型</t>
+          <t>總傷害加成</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>影響戰鬥訊息的用字，例如「割傷」會顯示「造成一道輕微的傷口」之類。</t>
+          <t>自動計算 = 整套加成 + 招式加成。</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>割傷（刀）</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
+          <t>（自動）</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr"/>
+      <c r="E25" s="19" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>元素</t>
+          <t>傷害類型</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>招式帶火、冰、雷、風屬性時，打中後會再加上裝備的同元素傷害。</t>
+          <t>影響戰鬥訊息的用字，例如「割傷」會顯示「造成一道輕微的傷口」之類。</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
@@ -10979,7 +11188,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>無</t>
+          <t>割傷（刀）</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -10991,49 +11200,49 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>出招權重</t>
+          <t>元素</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>這招被選中的機率。5 是普通，10 是很常出，1 是很少出。</t>
+          <t>招式帶火、冰、雷、風屬性時，打中後會再加上裝備的同元素傷害。</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>1～10</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>無</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>有</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>出招條件</t>
+          <t>出招權重</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>只在特定情況才會出的招，例如對手重傷時的殺招、格擋成功後的反擊。</t>
+          <t>這招被選中的機率。5 是普通，10 是很常出，1 是很少出。</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>1～10</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>無（隨時都可能出）</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -11045,68 +11254,68 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>連招前置</t>
+          <t>出招條件</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>出招條件選「連招」時才需要填：最近幾回合內要先用過哪些招，用逗號分隔。</t>
+          <t>只在特定情況才會出的招，例如對手重傷時的殺招、格擋成功後的反擊。</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>招式名</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr"/>
-      <c r="E29" s="19" t="inlineStr"/>
+          <t>下拉選單</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>無（隨時都可能出）</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>內力消耗</t>
+          <t>連招前置</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>使出這招要扣多少內力。內力不夠就不會出這招。</t>
+          <t>出招條件選「連招」時才需要填：最近幾回合內要先用過哪些招，用逗號分隔。</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>0～500</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+          <t>招式名</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>冷卻</t>
+          <t>內力消耗</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>使出後要隔幾回合才能再出。</t>
+          <t>使出這招要扣多少內力。內力不夠就不會出這招。</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>0～20</t>
+          <t>0～500</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>0（沒有冷卻）</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -11118,22 +11327,22 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>冷卻</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>打中後的附加效果，見下方特效說明。</t>
+          <t>使出後要隔幾回合才能再出。</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>下拉選單</t>
+          <t>0～20</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>無</t>
+          <t>0（沒有冷卻）</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -11145,22 +11354,22 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>特效機率</t>
+          <t>特效</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>打中時發動特效的機率。</t>
+          <t>打中後的附加效果，見下方特效說明。</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
+          <t>下拉選單</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>無</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -11172,22 +11381,22 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>特效持續</t>
+          <t>特效機率</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>特效持續幾回合（追擊、震退這類一次性的不用填）。</t>
+          <t>打中時發動特效的機率。</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>0～20</t>
+          <t>0～100</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -11199,22 +11408,22 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>特效強度</t>
+          <t>特效持續</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>依特效不同意思不同，見下方。</t>
+          <t>特效持續幾回合（追擊、震退這類一次性的不用填）。</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>0～100</t>
+          <t>0～20</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>依特效</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
@@ -11226,57 +11435,69 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
+          <t>特效強度</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>依特效不同意思不同，見下方。</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>0～100</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>依特效</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>任何想說明的事。</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr"/>
-      <c r="E36" s="19" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr"/>
+      <c r="E37" s="19" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>【特效說明】</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr"/>
-      <c r="C37" s="18" t="inlineStr"/>
-      <c r="D37" s="18" t="inlineStr"/>
-      <c r="E37" s="18" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>流血</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>每回合扣血。強度 = 每回合扣多少點。</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr"/>
-      <c r="D38" s="19" t="inlineStr"/>
-      <c r="E38" s="19" t="inlineStr"/>
+      <c r="B38" s="17" t="inlineStr"/>
+      <c r="C38" s="18" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr"/>
+      <c r="E38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>破防</t>
+          <t>流血</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>對手防具效果降低。強度 = 降低幾 %。</t>
+          <t>每回合扣血。強度 = 每回合扣多少點。</t>
         </is>
       </c>
       <c r="C39" s="19" t="inlineStr"/>
@@ -11286,12 +11507,12 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>暈眩</t>
+          <t>破防</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>對手停手不能出招。強度不用填。</t>
+          <t>對手防具效果降低。強度 = 降低幾 %。</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr"/>
@@ -11301,12 +11522,12 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>緩速</t>
+          <t>暈眩</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>對手出招變慢、閃躲降低。強度 = 降低幾 %。</t>
+          <t>對手停手不能出招。強度不用填。</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr"/>
@@ -11316,12 +11537,12 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>吸血</t>
+          <t>緩速</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>打中時回復自己的氣。強度 = 回復傷害的幾 %。</t>
+          <t>對手出招變慢、閃躲降低。強度 = 降低幾 %。</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr"/>
@@ -11331,12 +11552,12 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>追擊</t>
+          <t>吸血</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>立刻再出一招（像瘋虎刀法的追擊）。強度 = 追擊招的傷害 %，100 = 一般傷害。</t>
+          <t>打中時回復自己的氣。強度 = 回復傷害的幾 %。</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr"/>
@@ -11346,17 +11567,32 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>震退</t>
+          <t>追擊</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>讓對手忙亂一回合。強度不用填。</t>
+          <t>立刻再出一招（像瘋虎刀法的追擊）。強度 = 追擊招的傷害 %，100 = 一般傷害。</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr"/>
       <c r="D44" s="19" t="inlineStr"/>
       <c r="E44" s="19" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>震退</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>讓對手忙亂一回合。強度不用填。</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr"/>
+      <c r="D45" s="19" t="inlineStr"/>
+      <c r="E45" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/martial_arts/武功強度設定表.xlsx
+++ b/docs/martial_arts/武功強度設定表.xlsx
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="H2" s="8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>30</v>
@@ -839,7 +839,7 @@
         <v>11</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>武功每升一級，給「武術造詣」= 新等級 × 係數。（龍圖心經用 10；三門刀法定案 100）</t>
+          <t>武功每升一級，給「武術造詣」= 新等級 × 係數。（龍圖心經用 10；三門刀法定案 10）</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>給「武學之道」=（新等級 − 減數）× 係數。（龍圖心經：起始 51、減數 41、係數 10；三門刀法定案：起始 30、減數 11、係數 75）</t>
+          <t>給「武學之道」=（新等級 − 減數）× 係數。（龍圖心經：起始 51、減數 41、係數 10；三門刀法定案：起始 30、減數 11、係數 10）</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">

--- a/docs/martial_arts/武功強度設定表.xlsx
+++ b/docs/martial_arts/武功強度設定表.xlsx
@@ -836,7 +836,7 @@
         <v>30</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K2" s="8" t="n">
         <v>10</v>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>給「武學之道」=（新等級 − 減數）× 係數。（龍圖心經：起始 51、減數 41、係數 10；三門刀法定案：起始 30、減數 11、係數 10）</t>
+          <t>給「武學之道」=（新等級 − 減數）× 係數。（龍圖心經：起始 51、減數 41、係數 10；三門刀法定案：起始 30、減數 29、係數 10）</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
